--- a/ro-crate/ro-crate-metadata.xlsx
+++ b/ro-crate/ro-crate-metadata.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="338">
   <si>
     <t>Name</t>
   </si>
@@ -92,7 +92,7 @@
     <t>pcdm:hasMember</t>
   </si>
   <si>
-    <t>["arcp://name,AnonymisingELANFiles", "arcp://name,CollocationAnalyser", "arcp://name,CollocationCalculator", "arcp://name,ConcordanceExplorer", "arcp://name,Concordancer", "arcp://name,Crate-O", "arcp://name,Discursis", "arcp://name,DocumentSimilarity", "arcp://name,ELANAnnotationSplitter", "arcp://name,ELANAudioSegmentation", "arcp://name,ELANCommander", "arcp://name,ELANInventory", "arcp://name,ELANReplacer", "arcp://name,FileRenamer", "arcp://name,ImageDatasetExplorer", "arcp://name,KeywordFinder", "arcp://name,KeywordExtractor", "arcp://name,KeywordsAnalysis", "arcp://name,Lameta", "arcp://name,NetworkVisualiser", "arcp://name,Part-of-SpeechTagger", "arcp://name,POSTagger", "arcp://name,QuotationTool", "arcp://name,SemanticTaggerEnglish", "arcp://name,SentimentExplorer", "arcp://name,SentimentExplorerbrowser-based", "arcp://name,TextCleaner", "arcp://name,TextCleanerbrowser-based", "arcp://name,TopicExplorer", "arcp://name,TopicDetector", "arcp://name,WordFinder", "arcp://name,WordWebber", "https://data.ldaca.edu.au/object?_id=https://github.com/Australian-Text-Analytics-Platform/cooee/blob/main/cooee.ipynb", "https://github.com/Australian-Text-Analytics-Platform/farms-to-freeways", "https://data.ldaca.edu.au/object?_id=https%3A%2F%2Fgithub.com%2FAustralian-Text-Analytics-Platform%2Fnotebook-ausreddit%2Fblob%2Fmain%2Fexploration.ipynb", "https://data.ldaca.edu.au/object?_id=https%3A%2F%2Fgithub.com%2FAustralian-Text-Analytics-Platform%2Fnotebook-twittersphere%2Fblob%2Fmain%2Fexploration.ipynb"]</t>
+    <t>["arcp://name,AnonymisingELANFiles", "arcp://name,CollocationAnalyser", "arcp://name,CollocationCalculator", "arcp://name,ConcordanceExplorer", "arcp://name,Concordancer", "arcp://name,Crate-O", "arcp://name,Discursis", "arcp://name,DocumentSimilarity", "arcp://name,ELANAnnotationSplitter", "arcp://name,ELANAudioSegmentation", "arcp://name,ELANCommander", "arcp://name,ELANInventory", "arcp://name,ELANReplacer", "arcp://name,FileRenamer", "arcp://name,ImageDatasetExplorer", "arcp://name,KeywordFinder", "arcp://name,KeywordExtractor", "arcp://name,KeywordsAnalysis", "arcp://name,Lameta", "arcp://name,NetworkVisualiser", "arcp://name,Part-of-SpeechTagger", "arcp://name,POSTagger", "arcp://name,QuotationTool", "arcp://name,SemanticTaggerEnglish", "arcp://name,SentimentExplorer", "arcp://name,SentimentExplorerbrowser-based", "arcp://name,TextCleaner", "arcp://name,TextCleanerbrowser-based", "arcp://name,TopicExplorer", "arcp://name,TopicDetector", "arcp://name,WordFinder", "arcp://name,WordWebber", "arcp://name,TopSBM", "arcp://name,SemanticTaggermultilingual", "https://data.ldaca.edu.au/object?_id=https://github.com/Australian-Text-Analytics-Platform/cooee/blob/main/cooee.ipynb", "https://github.com/Australian-Text-Analytics-Platform/farms-to-freeways", "https://data.ldaca.edu.au/object?_id=https%3A%2F%2Fgithub.com%2FAustralian-Text-Analytics-Platform%2Fnotebook-ausreddit%2Fblob%2Fmain%2Fexploration.ipynb", "https://data.ldaca.edu.au/object?_id=https%3A%2F%2Fgithub.com%2FAustralian-Text-Analytics-Platform%2Fnotebook-twittersphere%2Fblob%2Fmain%2Fexploration.ipynb"]</t>
   </si>
   <si>
     <t>hasPart</t>
@@ -536,7 +536,7 @@
     <t>https://raw.githubusercontent.com/Australian-Text-Analytics-Platform/discursis/master/docs/Discursis%20User%20Guide.pdf</t>
   </si>
   <si>
-    <t>Not provided</t>
+    <t>object Object</t>
   </si>
   <si>
     <t>Based on Angus et al</t>
@@ -735,9 +735,6 @@
     <t>https://www.elararchive.org/uncategorized/SO_7557c4dd-1c83-485c-b95c-c0a292cfc42c/</t>
   </si>
   <si>
-    <t>object Object</t>
-  </si>
-  <si>
     <t>arcp://name,NetworkVisualiser</t>
   </si>
   <si>
@@ -813,6 +810,9 @@
     <t>https://github.com/Australian-Text-Analytics-Platform/semantic-tagger/blob/main/documents/semtag_help_pages.pdf</t>
   </si>
   <si>
+    <t>Jufri, Sony &amp; Sun, Chao (2022). Semantic Tagger. v1.0. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/semantic-tagger</t>
+  </si>
+  <si>
     <t>arcp://name,SentimentExplorer</t>
   </si>
   <si>
@@ -898,6 +898,36 @@
   </si>
   <si>
     <t>"images/word-webber.png"</t>
+  </si>
+  <si>
+    <t>arcp://name,TopSBM</t>
+  </si>
+  <si>
+    <t>TopSBM</t>
+  </si>
+  <si>
+    <t>"https://orcid.org/0000-0002-1428-2649"</t>
+  </si>
+  <si>
+    <t>https://github.com/Australian-Text-Analytics-Platform/topsbm</t>
+  </si>
+  <si>
+    <t>Topic modelling approach that infers a hierarchy of topic clusters and word clusters in your Corpus in a non-parametric manner by leveraging stochastic block models.</t>
+  </si>
+  <si>
+    <t>arcp://name,SemanticTaggermultilingual</t>
+  </si>
+  <si>
+    <t>Semantic Tagger (multilingual)</t>
+  </si>
+  <si>
+    <t>https://github.com/Australian-Text-Analytics-Platform/semantic-tagger/tree/multi-lingual</t>
+  </si>
+  <si>
+    <t>With the multilingual Semantic Tagger, you can use Python Multilingual Ucrel Semantic Analysis System (PyMUSAS) to tag your text so you can extract token level semantic tags from the tagged text. Supports Chinese, Italian and Spanish languages.</t>
+  </si>
+  <si>
+    <t>https://github.com/Australian-Text-Analytics-Platform/semantic-tagger/blob/multi-lingual/documents/semtag_help_pages.pdf</t>
   </si>
   <si>
     <t>https://data.ldaca.edu.au/object?_id=https://github.com/Australian-Text-Analytics-Platform/cooee/blob/main/cooee.ipynb</t>
@@ -2136,7 +2166,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S37"/>
+  <dimension ref="A1:S39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="19" width="20" customWidth="1"/>
@@ -3016,12 +3046,12 @@
         <v>237</v>
       </c>
       <c r="P20" t="s">
-        <v>238</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B21" t="s">
         <v>120</v>
@@ -3033,7 +3063,7 @@
         <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
@@ -3051,18 +3081,18 @@
         <v>134</v>
       </c>
       <c r="K21" t="s">
+        <v>240</v>
+      </c>
+      <c r="L21" t="s">
         <v>241</v>
       </c>
-      <c r="L21" t="s">
+      <c r="Q21" t="s">
         <v>242</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s">
         <v>120</v>
@@ -3074,7 +3104,7 @@
         <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
@@ -3092,7 +3122,7 @@
         <v>134</v>
       </c>
       <c r="K22" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L22" t="s">
         <v>136</v>
@@ -3100,7 +3130,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B23" t="s">
         <v>120</v>
@@ -3112,7 +3142,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
@@ -3130,18 +3160,18 @@
         <v>140</v>
       </c>
       <c r="K23" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L23" t="s">
         <v>136</v>
       </c>
       <c r="N23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s">
         <v>120</v>
@@ -3153,7 +3183,7 @@
         <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F24" t="s">
         <v>13</v>
@@ -3168,30 +3198,30 @@
         <v>125</v>
       </c>
       <c r="J24" t="s">
+        <v>252</v>
+      </c>
+      <c r="K24" t="s">
         <v>253</v>
-      </c>
-      <c r="K24" t="s">
-        <v>254</v>
       </c>
       <c r="L24" t="s">
         <v>152</v>
       </c>
       <c r="M24" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="N24" t="s">
+        <v>254</v>
+      </c>
+      <c r="O24" t="s">
         <v>255</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>256</v>
-      </c>
-      <c r="P24" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s">
         <v>120</v>
@@ -3203,7 +3233,7 @@
         <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
@@ -3218,25 +3248,25 @@
         <v>125</v>
       </c>
       <c r="J25" t="s">
+        <v>259</v>
+      </c>
+      <c r="K25" t="s">
         <v>260</v>
-      </c>
-      <c r="K25" t="s">
-        <v>261</v>
       </c>
       <c r="L25" t="s">
         <v>152</v>
       </c>
       <c r="M25" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="N25" t="s">
+        <v>261</v>
+      </c>
+      <c r="O25" t="s">
         <v>262</v>
       </c>
-      <c r="O25" t="s">
+      <c r="P25" t="s">
         <v>263</v>
-      </c>
-      <c r="P25" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -3552,16 +3582,16 @@
         <v>291</v>
       </c>
       <c r="L33" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="N33" t="s">
         <v>292</v>
       </c>
       <c r="Q33" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>293</v>
       </c>
@@ -3569,175 +3599,260 @@
         <v>120</v>
       </c>
       <c r="C34" t="s">
+        <v>121</v>
+      </c>
+      <c r="D34" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" t="s">
         <v>294</v>
-      </c>
-      <c r="D34" t="s">
-        <v>34</v>
-      </c>
-      <c r="E34" t="s">
-        <v>295</v>
       </c>
       <c r="F34" t="s">
         <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="H34" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I34" t="s">
         <v>125</v>
       </c>
       <c r="J34" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K34" t="s">
         <v>297</v>
       </c>
-      <c r="M34" t="s">
+      <c r="L34" t="s">
+        <v>152</v>
+      </c>
+      <c r="P34" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>298</v>
-      </c>
-      <c r="R34" t="s">
-        <v>299</v>
-      </c>
-      <c r="S34" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>301</v>
       </c>
       <c r="B35" t="s">
         <v>120</v>
       </c>
       <c r="C35" t="s">
-        <v>294</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
         <v>34</v>
       </c>
       <c r="E35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F35" t="s">
-        <v>303</v>
+        <v>13</v>
       </c>
       <c r="G35" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="H35" t="s">
-        <v>304</v>
+        <v>176</v>
       </c>
       <c r="I35" t="s">
         <v>125</v>
       </c>
       <c r="J35" t="s">
+        <v>300</v>
+      </c>
+      <c r="K35" t="s">
         <v>301</v>
       </c>
       <c r="L35" t="s">
-        <v>305</v>
-      </c>
-      <c r="M35" t="s">
-        <v>301</v>
-      </c>
-      <c r="R35" t="s">
-        <v>306</v>
-      </c>
-      <c r="S35" t="s">
-        <v>300</v>
+        <v>152</v>
+      </c>
+      <c r="O35" t="s">
+        <v>302</v>
+      </c>
+      <c r="P35" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B36" t="s">
         <v>120</v>
       </c>
       <c r="C36" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="D36" t="s">
         <v>34</v>
       </c>
       <c r="E36" t="s">
-        <v>308</v>
+        <v>305</v>
+      </c>
+      <c r="F36" t="s">
+        <v>13</v>
       </c>
       <c r="G36" t="s">
-        <v>309</v>
+        <v>123</v>
       </c>
       <c r="H36" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="I36" t="s">
         <v>125</v>
       </c>
       <c r="J36" t="s">
+        <v>303</v>
+      </c>
+      <c r="K36" t="s">
         <v>307</v>
       </c>
-      <c r="K36" t="s">
-        <v>311</v>
-      </c>
-      <c r="L36" t="s">
-        <v>312</v>
-      </c>
       <c r="M36" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="R36" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="S36" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B37" t="s">
         <v>120</v>
       </c>
       <c r="C37" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="D37" t="s">
         <v>34</v>
       </c>
       <c r="E37" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>313</v>
       </c>
       <c r="G37" t="s">
-        <v>309</v>
+        <v>123</v>
       </c>
       <c r="H37" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="I37" t="s">
         <v>125</v>
       </c>
       <c r="J37" t="s">
+        <v>311</v>
+      </c>
+      <c r="L37" t="s">
         <v>315</v>
       </c>
-      <c r="K37" t="s">
+      <c r="M37" t="s">
+        <v>311</v>
+      </c>
+      <c r="R37" t="s">
+        <v>316</v>
+      </c>
+      <c r="S37" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>317</v>
       </c>
-      <c r="L37" t="s">
-        <v>312</v>
-      </c>
-      <c r="M37" t="s">
+      <c r="B38" t="s">
+        <v>120</v>
+      </c>
+      <c r="C38" t="s">
+        <v>304</v>
+      </c>
+      <c r="D38" t="s">
+        <v>34</v>
+      </c>
+      <c r="E38" t="s">
         <v>318</v>
       </c>
-      <c r="R37" t="s">
+      <c r="G38" t="s">
         <v>319</v>
       </c>
-      <c r="S37" t="s">
-        <v>300</v>
+      <c r="H38" t="s">
+        <v>320</v>
+      </c>
+      <c r="I38" t="s">
+        <v>125</v>
+      </c>
+      <c r="J38" t="s">
+        <v>317</v>
+      </c>
+      <c r="K38" t="s">
+        <v>321</v>
+      </c>
+      <c r="L38" t="s">
+        <v>322</v>
+      </c>
+      <c r="M38" t="s">
+        <v>323</v>
+      </c>
+      <c r="R38" t="s">
+        <v>324</v>
+      </c>
+      <c r="S38" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>325</v>
+      </c>
+      <c r="B39" t="s">
+        <v>120</v>
+      </c>
+      <c r="C39" t="s">
+        <v>304</v>
+      </c>
+      <c r="D39" t="s">
+        <v>34</v>
+      </c>
+      <c r="E39" t="s">
+        <v>326</v>
+      </c>
+      <c r="F39" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" t="s">
+        <v>319</v>
+      </c>
+      <c r="H39" t="s">
+        <v>320</v>
+      </c>
+      <c r="I39" t="s">
+        <v>125</v>
+      </c>
+      <c r="J39" t="s">
+        <v>325</v>
+      </c>
+      <c r="K39" t="s">
+        <v>327</v>
+      </c>
+      <c r="L39" t="s">
+        <v>322</v>
+      </c>
+      <c r="M39" t="s">
+        <v>328</v>
+      </c>
+      <c r="R39" t="s">
+        <v>329</v>
+      </c>
+      <c r="S39" t="s">
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -3767,46 +3882,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="B2" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="C2" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="B3" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="C3" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="B4" t="s">
-        <v>238</v>
+        <v>172</v>
       </c>
       <c r="C4" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B5" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C5" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>

--- a/ro-crate/ro-crate-metadata.xlsx
+++ b/ro-crate/ro-crate-metadata.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="340">
   <si>
     <t>Name</t>
   </si>
@@ -261,6 +261,12 @@
   </si>
   <si>
     <t>Simon Musgrave</t>
+  </si>
+  <si>
+    <t>#HuenHeiChan</t>
+  </si>
+  <si>
+    <t>Huen Hei (Jack) Chan</t>
   </si>
   <si>
     <t>https://github.com/Language-Research-Technology</t>
@@ -906,7 +912,7 @@
     <t>TopSBM</t>
   </si>
   <si>
-    <t>"https://orcid.org/0000-0002-1428-2649"</t>
+    <t>["#HuenHeiChan", "https://orcid.org/0000-0002-1932-3710"]</t>
   </si>
   <si>
     <t>https://github.com/Australian-Text-Analytics-Platform/topsbm</t>
@@ -1798,7 +1804,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="20" customWidth="1"/>
@@ -1967,6 +1973,17 @@
       </c>
       <c r="C15" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1996,112 +2013,112 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" t="s">
         <v>84</v>
       </c>
-      <c r="B3" t="s">
-        <v>82</v>
-      </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -2132,7 +2149,7 @@
         <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F1" t="s">
         <v>31</v>
@@ -2140,16 +2157,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -2180,10 +2197,10 @@
         <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E1" t="s">
         <v>6</v>
@@ -2198,1661 +2215,1661 @@
         <v>17</v>
       </c>
       <c r="I1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K1" t="s">
         <v>8</v>
       </c>
       <c r="L1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="N1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="P1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="R1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="S1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D2" t="s">
         <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L2" t="s">
+        <v>130</v>
+      </c>
+      <c r="M2" t="s">
         <v>128</v>
-      </c>
-      <c r="M2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D3" t="s">
         <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D4" t="s">
         <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D6" t="s">
         <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="L6" t="s">
+        <v>154</v>
+      </c>
+      <c r="M6" t="s">
         <v>152</v>
       </c>
-      <c r="M6" t="s">
-        <v>150</v>
-      </c>
       <c r="N6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="P6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D7" t="s">
         <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J7" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L7" t="s">
+        <v>164</v>
+      </c>
+      <c r="M7" t="s">
         <v>162</v>
       </c>
-      <c r="M7" t="s">
-        <v>160</v>
-      </c>
       <c r="N7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D8" t="s">
         <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L8" t="s">
+        <v>171</v>
+      </c>
+      <c r="M8" t="s">
         <v>169</v>
       </c>
-      <c r="M8" t="s">
-        <v>167</v>
-      </c>
       <c r="N8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="P8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D9" t="s">
         <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="O9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D10" t="s">
         <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D11" t="s">
         <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I11" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J11" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M11" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D12" t="s">
         <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J12" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K12" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D13" t="s">
         <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J13" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D14" t="s">
         <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I14" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J14" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K14" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L14" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M14" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D15" t="s">
         <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N15" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B16" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D16" t="s">
         <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H16" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I16" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J16" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K16" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L16" t="s">
+        <v>214</v>
+      </c>
+      <c r="M16" t="s">
         <v>212</v>
       </c>
-      <c r="M16" t="s">
-        <v>210</v>
-      </c>
       <c r="N16" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B17" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C17" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D17" t="s">
         <v>34</v>
       </c>
       <c r="E17" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
       </c>
       <c r="G17" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H17" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I17" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J17" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K17" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L17" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B18" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D18" t="s">
         <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H18" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K18" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L18" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N18" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B19" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C19" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D19" t="s">
         <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H19" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J19" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K19" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L19" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M19" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N19" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O19" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P19" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D20" t="s">
         <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H20" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I20" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J20" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K20" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L20" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M20" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N20" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="O20" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P20" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C21" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D21" t="s">
         <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H21" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I21" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J21" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K21" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L21" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q21" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C22" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D22" t="s">
         <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
       </c>
       <c r="G22" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H22" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I22" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J22" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K22" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L22" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D23" t="s">
         <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
       </c>
       <c r="G23" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H23" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I23" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J23" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K23" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L23" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N23" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D24" t="s">
         <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F24" t="s">
         <v>13</v>
       </c>
       <c r="G24" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H24" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I24" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J24" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="K24" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="L24" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M24" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N24" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O24" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P24" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B25" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C25" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D25" t="s">
         <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H25" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I25" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K25" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L25" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N25" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O25" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P25" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
         <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
       </c>
       <c r="G26" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H26" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I26" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J26" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K26" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L26" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D27" t="s">
         <v>34</v>
       </c>
       <c r="E27" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
       </c>
       <c r="G27" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H27" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I27" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J27" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K27" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L27" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N27" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D28" t="s">
         <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
       </c>
       <c r="G28" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H28" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I28" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J28" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K28" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="L28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D29" t="s">
         <v>34</v>
       </c>
       <c r="E29" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
       </c>
       <c r="G29" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H29" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I29" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J29" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K29" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="L29" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N29" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B30" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C30" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D30" t="s">
         <v>34</v>
       </c>
       <c r="E30" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
       </c>
       <c r="G30" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H30" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I30" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K30" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D31" t="s">
         <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F31" t="s">
         <v>13</v>
       </c>
       <c r="G31" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H31" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I31" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J31" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K31" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N31" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B32" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D32" t="s">
         <v>34</v>
       </c>
       <c r="E32" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H32" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I32" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J32" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K32" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L32" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N32" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D33" t="s">
         <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F33" t="s">
         <v>13</v>
       </c>
       <c r="G33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I33" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K33" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L33" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N33" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q33" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D34" t="s">
         <v>34</v>
       </c>
       <c r="E34" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F34" t="s">
         <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H34" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="I34" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L34" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P34" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B35" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D35" t="s">
         <v>34</v>
       </c>
       <c r="E35" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F35" t="s">
         <v>13</v>
       </c>
       <c r="G35" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H35" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I35" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J35" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="K35" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L35" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O35" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="P35" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B36" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C36" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D36" t="s">
         <v>34</v>
       </c>
       <c r="E36" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F36" t="s">
         <v>13</v>
       </c>
       <c r="G36" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H36" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I36" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J36" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="K36" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M36" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="R36" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="S36" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B37" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C37" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D37" t="s">
         <v>34</v>
       </c>
       <c r="E37" t="s">
+        <v>314</v>
+      </c>
+      <c r="F37" t="s">
+        <v>315</v>
+      </c>
+      <c r="G37" t="s">
+        <v>125</v>
+      </c>
+      <c r="H37" t="s">
+        <v>316</v>
+      </c>
+      <c r="I37" t="s">
+        <v>127</v>
+      </c>
+      <c r="J37" t="s">
+        <v>313</v>
+      </c>
+      <c r="L37" t="s">
+        <v>317</v>
+      </c>
+      <c r="M37" t="s">
+        <v>313</v>
+      </c>
+      <c r="R37" t="s">
+        <v>318</v>
+      </c>
+      <c r="S37" t="s">
         <v>312</v>
-      </c>
-      <c r="F37" t="s">
-        <v>313</v>
-      </c>
-      <c r="G37" t="s">
-        <v>123</v>
-      </c>
-      <c r="H37" t="s">
-        <v>314</v>
-      </c>
-      <c r="I37" t="s">
-        <v>125</v>
-      </c>
-      <c r="J37" t="s">
-        <v>311</v>
-      </c>
-      <c r="L37" t="s">
-        <v>315</v>
-      </c>
-      <c r="M37" t="s">
-        <v>311</v>
-      </c>
-      <c r="R37" t="s">
-        <v>316</v>
-      </c>
-      <c r="S37" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B38" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D38" t="s">
         <v>34</v>
       </c>
       <c r="E38" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G38" t="s">
+        <v>321</v>
+      </c>
+      <c r="H38" t="s">
+        <v>322</v>
+      </c>
+      <c r="I38" t="s">
+        <v>127</v>
+      </c>
+      <c r="J38" t="s">
         <v>319</v>
       </c>
-      <c r="H38" t="s">
-        <v>320</v>
-      </c>
-      <c r="I38" t="s">
-        <v>125</v>
-      </c>
-      <c r="J38" t="s">
-        <v>317</v>
-      </c>
       <c r="K38" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L38" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M38" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="R38" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="S38" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B39" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C39" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D39" t="s">
         <v>34</v>
       </c>
       <c r="E39" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F39" t="s">
         <v>13</v>
       </c>
       <c r="G39" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H39" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I39" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J39" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K39" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L39" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M39" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="R39" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="S39" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -3882,46 +3899,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C3" t="s">
         <v>334</v>
-      </c>
-      <c r="C3" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B5" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C5" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>

--- a/ro-crate/ro-crate-metadata.xlsx
+++ b/ro-crate/ro-crate-metadata.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="342">
   <si>
     <t>Name</t>
   </si>
@@ -267,6 +267,12 @@
   </si>
   <si>
     <t>Huen Hei (Jack) Chan</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0002-1932-3710</t>
+  </si>
+  <si>
+    <t>Eduardo G. Altmann</t>
   </si>
   <si>
     <t>https://github.com/Language-Research-Technology</t>
@@ -1804,7 +1810,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="20" customWidth="1"/>
@@ -1984,6 +1990,17 @@
       </c>
       <c r="C16" t="s">
         <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -2013,112 +2030,112 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" t="s">
         <v>86</v>
       </c>
-      <c r="B3" t="s">
-        <v>84</v>
-      </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2149,7 +2166,7 @@
         <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F1" t="s">
         <v>31</v>
@@ -2157,16 +2174,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -2197,10 +2214,10 @@
         <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E1" t="s">
         <v>6</v>
@@ -2215,1661 +2232,1661 @@
         <v>17</v>
       </c>
       <c r="I1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K1" t="s">
         <v>8</v>
       </c>
       <c r="L1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="N1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="P1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="Q1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="S1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
         <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L2" t="s">
+        <v>132</v>
+      </c>
+      <c r="M2" t="s">
         <v>130</v>
-      </c>
-      <c r="M2" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D3" t="s">
         <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D4" t="s">
         <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D6" t="s">
         <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L6" t="s">
+        <v>156</v>
+      </c>
+      <c r="M6" t="s">
         <v>154</v>
       </c>
-      <c r="M6" t="s">
-        <v>152</v>
-      </c>
       <c r="N6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="O6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D7" t="s">
         <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I7" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L7" t="s">
+        <v>166</v>
+      </c>
+      <c r="M7" t="s">
         <v>164</v>
       </c>
-      <c r="M7" t="s">
-        <v>162</v>
-      </c>
       <c r="N7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D8" t="s">
         <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="L8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M8" t="s">
         <v>171</v>
       </c>
-      <c r="M8" t="s">
-        <v>169</v>
-      </c>
       <c r="N8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="P8" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D9" t="s">
         <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I9" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="L9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="N9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="P9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D10" t="s">
         <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D11" t="s">
         <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K11" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L11" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D12" t="s">
         <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I12" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J12" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K12" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D13" t="s">
         <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H13" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="K13" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D14" t="s">
         <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H14" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I14" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J14" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K14" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L14" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M14" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D15" t="s">
         <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I15" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L15" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B16" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C16" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D16" t="s">
         <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H16" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I16" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J16" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K16" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L16" t="s">
+        <v>216</v>
+      </c>
+      <c r="M16" t="s">
         <v>214</v>
       </c>
-      <c r="M16" t="s">
-        <v>212</v>
-      </c>
       <c r="N16" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B17" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D17" t="s">
         <v>34</v>
       </c>
       <c r="E17" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
       </c>
       <c r="G17" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H17" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I17" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J17" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K17" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L17" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B18" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C18" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D18" t="s">
         <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H18" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I18" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J18" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K18" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N18" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C19" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D19" t="s">
         <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H19" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I19" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J19" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K19" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="L19" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M19" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N19" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="O19" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="P19" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
         <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H20" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I20" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J20" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K20" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L20" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M20" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="N20" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O20" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P20" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B21" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D21" t="s">
         <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H21" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I21" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J21" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K21" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L21" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q21" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D22" t="s">
         <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
       </c>
       <c r="G22" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H22" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I22" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J22" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K22" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L22" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C23" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
         <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
       </c>
       <c r="G23" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H23" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I23" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J23" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K23" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L23" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N23" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C24" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D24" t="s">
         <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F24" t="s">
         <v>13</v>
       </c>
       <c r="G24" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H24" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I24" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J24" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K24" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L24" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M24" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N24" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O24" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P24" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C25" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D25" t="s">
         <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H25" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I25" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J25" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K25" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L25" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M25" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N25" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="O25" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P25" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B26" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C26" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D26" t="s">
         <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
       </c>
       <c r="G26" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H26" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I26" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J26" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K26" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L26" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B27" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C27" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D27" t="s">
         <v>34</v>
       </c>
       <c r="E27" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
       </c>
       <c r="G27" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H27" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I27" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J27" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K27" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L27" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N27" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B28" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C28" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D28" t="s">
         <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
       </c>
       <c r="G28" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H28" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I28" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K28" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B29" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D29" t="s">
         <v>34</v>
       </c>
       <c r="E29" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
       </c>
       <c r="G29" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H29" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I29" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J29" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K29" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L29" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N29" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D30" t="s">
         <v>34</v>
       </c>
       <c r="E30" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
       </c>
       <c r="G30" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K30" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L30" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B31" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D31" t="s">
         <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F31" t="s">
         <v>13</v>
       </c>
       <c r="G31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H31" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I31" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J31" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K31" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N31" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B32" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D32" t="s">
         <v>34</v>
       </c>
       <c r="E32" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H32" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K32" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N32" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D33" t="s">
         <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F33" t="s">
         <v>13</v>
       </c>
       <c r="G33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I33" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J33" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K33" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L33" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N33" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q33" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C34" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D34" t="s">
         <v>34</v>
       </c>
       <c r="E34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F34" t="s">
         <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I34" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J34" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K34" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="L34" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="P34" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C35" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D35" t="s">
         <v>34</v>
       </c>
       <c r="E35" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F35" t="s">
         <v>13</v>
       </c>
       <c r="G35" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H35" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I35" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J35" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K35" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L35" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O35" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P35" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B36" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C36" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D36" t="s">
         <v>34</v>
       </c>
       <c r="E36" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F36" t="s">
         <v>13</v>
       </c>
       <c r="G36" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H36" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I36" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J36" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K36" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M36" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="R36" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="S36" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C37" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D37" t="s">
         <v>34</v>
       </c>
       <c r="E37" t="s">
+        <v>316</v>
+      </c>
+      <c r="F37" t="s">
+        <v>317</v>
+      </c>
+      <c r="G37" t="s">
+        <v>127</v>
+      </c>
+      <c r="H37" t="s">
+        <v>318</v>
+      </c>
+      <c r="I37" t="s">
+        <v>129</v>
+      </c>
+      <c r="J37" t="s">
+        <v>315</v>
+      </c>
+      <c r="L37" t="s">
+        <v>319</v>
+      </c>
+      <c r="M37" t="s">
+        <v>315</v>
+      </c>
+      <c r="R37" t="s">
+        <v>320</v>
+      </c>
+      <c r="S37" t="s">
         <v>314</v>
-      </c>
-      <c r="F37" t="s">
-        <v>315</v>
-      </c>
-      <c r="G37" t="s">
-        <v>125</v>
-      </c>
-      <c r="H37" t="s">
-        <v>316</v>
-      </c>
-      <c r="I37" t="s">
-        <v>127</v>
-      </c>
-      <c r="J37" t="s">
-        <v>313</v>
-      </c>
-      <c r="L37" t="s">
-        <v>317</v>
-      </c>
-      <c r="M37" t="s">
-        <v>313</v>
-      </c>
-      <c r="R37" t="s">
-        <v>318</v>
-      </c>
-      <c r="S37" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C38" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D38" t="s">
         <v>34</v>
       </c>
       <c r="E38" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G38" t="s">
+        <v>323</v>
+      </c>
+      <c r="H38" t="s">
+        <v>324</v>
+      </c>
+      <c r="I38" t="s">
+        <v>129</v>
+      </c>
+      <c r="J38" t="s">
         <v>321</v>
       </c>
-      <c r="H38" t="s">
-        <v>322</v>
-      </c>
-      <c r="I38" t="s">
-        <v>127</v>
-      </c>
-      <c r="J38" t="s">
-        <v>319</v>
-      </c>
       <c r="K38" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L38" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M38" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="R38" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="S38" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B39" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C39" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D39" t="s">
         <v>34</v>
       </c>
       <c r="E39" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F39" t="s">
         <v>13</v>
       </c>
       <c r="G39" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H39" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I39" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J39" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K39" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L39" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M39" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="R39" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="S39" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -3899,46 +3916,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C3" t="s">
         <v>336</v>
-      </c>
-      <c r="C3" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C4" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C5" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>

--- a/ro-crate/ro-crate-metadata.xlsx
+++ b/ro-crate/ro-crate-metadata.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="350">
   <si>
     <t>Name</t>
   </si>
@@ -275,6 +275,24 @@
     <t>Eduardo G. Altmann</t>
   </si>
   <si>
+    <t>https://orcid.org/0000-0001-7819-5424</t>
+  </si>
+  <si>
+    <t>Monika Bednarek</t>
+  </si>
+  <si>
+    <t>#HamishCroser</t>
+  </si>
+  <si>
+    <t>Hamish Croser</t>
+  </si>
+  <si>
+    <t>#KristianMaras</t>
+  </si>
+  <si>
+    <t>Kristian Maras</t>
+  </si>
+  <si>
     <t>https://github.com/Language-Research-Technology</t>
   </si>
   <si>
@@ -338,6 +356,12 @@
     <t>Centre for Digital Cultures &amp; Societies</t>
   </si>
   <si>
+    <t>https://sydneycorpuslab.com/</t>
+  </si>
+  <si>
+    <t>Sydney Corpus Lab</t>
+  </si>
+  <si>
     <t>ldac:allowTextIndex</t>
   </si>
   <si>
@@ -476,63 +500,66 @@
     <t>Concordancer</t>
   </si>
   <si>
+    <t>["https://ror.org/0384j8v12", "https://github.com/Sydney-Informatics-Hub", "https://sydneycorpuslab.com/"]</t>
+  </si>
+  <si>
+    <t>["https://orcid.org/0000-0001-7819-5424", "https://orcid.org/0000-0002-3616-6235", "#KristianMaras", "#HamishCroser"]</t>
+  </si>
+  <si>
+    <t>https://github.com/Australian-Text-Analytics-Platform/atap_widgets</t>
+  </si>
+  <si>
+    <t>A concordancer that demos how to analyse turn-taking pairs in a concordancer</t>
+  </si>
+  <si>
+    <t>csv, xlsx, plain txt; also zip archive with the supported file formats</t>
+  </si>
+  <si>
+    <t>"images/concordancer.png"</t>
+  </si>
+  <si>
+    <t>https://github.com/Australian-Text-Analytics-Platform/atap_widgets/blob/main/docs/concordance_help_pages.pdf</t>
+  </si>
+  <si>
+    <t>Bednarek, M., Mather, M., Maras, K., &amp; Croser, H. (2023). ATAP Concordancer (v0.5.4) [Computer software]. https://github.com/Australian-Text-Analytics-Platform/atap_widgets. DOI. https://doi.org/10.5281/zenodo.10086731</t>
+  </si>
+  <si>
+    <t>arcp://name,Crate-O</t>
+  </si>
+  <si>
+    <t>Crate-O</t>
+  </si>
+  <si>
+    <t>["https://ror.org/00rqy9422", "https://github.com/Language-Research-Technology"]</t>
+  </si>
+  <si>
+    <t>"https://orcid.org/0000-0002-4438-2755"</t>
+  </si>
+  <si>
+    <t>https://github.com/Language-Research-Technology/crate-o</t>
+  </si>
+  <si>
+    <t>Browser-based editor for RO Crates</t>
+  </si>
+  <si>
+    <t>Various - text, video, audio, image, etc.</t>
+  </si>
+  <si>
+    <t>"images/crate-o.png"</t>
+  </si>
+  <si>
+    <t>https://www.ldaca.edu.au/resources/user-guides/crate-o/</t>
+  </si>
+  <si>
+    <t>arcp://name,Discursis</t>
+  </si>
+  <si>
+    <t>Discursis</t>
+  </si>
+  <si>
     <t>["https://ror.org/0384j8v12", "https://github.com/Sydney-Informatics-Hub"]</t>
   </si>
   <si>
-    <t>"https://orcid.org/0000-0002-3616-6235"</t>
-  </si>
-  <si>
-    <t>https://github.com/Australian-Text-Analytics-Platform/atap_widgets</t>
-  </si>
-  <si>
-    <t>A concordancer that demos how to analyse turn-taking pairs in a concordancer</t>
-  </si>
-  <si>
-    <t>csv, xlsx, plain txt; also zip archive with the supported file formats</t>
-  </si>
-  <si>
-    <t>"images/concordancer.png"</t>
-  </si>
-  <si>
-    <t>https://github.com/Australian-Text-Analytics-Platform/atap_widgets/blob/main/docs/concordance_help_pages.pdf</t>
-  </si>
-  <si>
-    <t>Bednarek, M., Mather, M., Maras, K., &amp; Croser, H. (2023). ATAP Concordancer (v0.5.4) [Computer software]. https://github.com/Australian-Text-Analytics-Platform/atap_widgets. DOI. https://doi.org/10.5281/zenodo.10086731</t>
-  </si>
-  <si>
-    <t>arcp://name,Crate-O</t>
-  </si>
-  <si>
-    <t>Crate-O</t>
-  </si>
-  <si>
-    <t>["https://ror.org/00rqy9422", "https://github.com/Language-Research-Technology"]</t>
-  </si>
-  <si>
-    <t>"https://orcid.org/0000-0002-4438-2755"</t>
-  </si>
-  <si>
-    <t>https://github.com/Language-Research-Technology/crate-o</t>
-  </si>
-  <si>
-    <t>Browser-based editor for RO Crates</t>
-  </si>
-  <si>
-    <t>Various - text, video, audio, image, etc.</t>
-  </si>
-  <si>
-    <t>"images/crate-o.png"</t>
-  </si>
-  <si>
-    <t>https://www.ldaca.edu.au/resources/user-guides/crate-o/</t>
-  </si>
-  <si>
-    <t>arcp://name,Discursis</t>
-  </si>
-  <si>
-    <t>Discursis</t>
-  </si>
-  <si>
     <t>https://github.com/Australian-Text-Analytics-Platform/discursis</t>
   </si>
   <si>
@@ -549,9 +576,6 @@
   </si>
   <si>
     <t>object Object</t>
-  </si>
-  <si>
-    <t>Based on Angus et al</t>
   </si>
   <si>
     <t>arcp://name,DocumentSimilarity</t>
@@ -1810,7 +1834,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="20" customWidth="1"/>
@@ -2003,6 +2027,39 @@
         <v>84</v>
       </c>
     </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2011,7 +2068,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="20" customWidth="1"/>
@@ -2030,112 +2087,123 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" t="s">
         <v>92</v>
       </c>
-      <c r="B5" t="s">
-        <v>86</v>
-      </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>112</v>
+      </c>
+      <c r="B12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2166,7 +2234,7 @@
         <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="F1" t="s">
         <v>31</v>
@@ -2174,16 +2242,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -2214,10 +2282,10 @@
         <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E1" t="s">
         <v>6</v>
@@ -2232,1661 +2300,1658 @@
         <v>17</v>
       </c>
       <c r="I1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="J1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="K1" t="s">
         <v>8</v>
       </c>
       <c r="L1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="M1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="N1" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="O1" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="P1" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="Q1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="R1" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="S1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D2" t="s">
         <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="H2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="I2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="J2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="K2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="L2" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="M2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" t="s">
         <v>133</v>
       </c>
-      <c r="B3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C3" t="s">
-        <v>125</v>
-      </c>
       <c r="D3" t="s">
         <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H3" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="J3" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="K3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="L3" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B4" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D4" t="s">
         <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H4" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I4" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="J4" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="K4" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="L4" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="N4" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C5" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H5" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I5" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="J5" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="K5" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="L5" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C6" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D6" t="s">
         <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H6" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="I6" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="J6" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="K6" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="L6" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="M6" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="N6" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="O6" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="P6" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C7" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D7" t="s">
         <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="H7" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I7" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="J7" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="K7" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="L7" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="M7" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="N7" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="O7" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B8" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C8" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D8" t="s">
         <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="I8" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="J8" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="K8" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="L8" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="M8" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="N8" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="O8" t="s">
-        <v>175</v>
-      </c>
-      <c r="P8" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="Q8" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B9" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D9" t="s">
         <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H9" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="I9" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="J9" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="K9" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="L9" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="M9" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="N9" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="O9" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="P9" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B10" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C10" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D10" t="s">
         <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="H10" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="I10" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="J10" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="K10" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="L10" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="M10" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D11" t="s">
         <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="H11" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="I11" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="J11" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="K11" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="L11" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="M11" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B12" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C12" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D12" t="s">
         <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="H12" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="I12" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="J12" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="K12" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="L12" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B13" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C13" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D13" t="s">
         <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="H13" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="I13" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="J13" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K13" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="L13" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="B14" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C14" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D14" t="s">
         <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="H14" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="I14" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="J14" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="K14" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="L14" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="M14" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B15" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C15" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D15" t="s">
         <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H15" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I15" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="J15" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="K15" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="L15" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="N15" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B16" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D16" t="s">
         <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H16" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I16" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="J16" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="K16" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="L16" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="M16" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="N16" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B17" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C17" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D17" t="s">
         <v>34</v>
       </c>
       <c r="E17" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
       </c>
       <c r="G17" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H17" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I17" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="J17" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="K17" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="L17" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B18" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C18" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D18" t="s">
         <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H18" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I18" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="J18" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="K18" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="L18" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="N18" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B19" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D19" t="s">
         <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H19" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="I19" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="J19" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="K19" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="L19" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="M19" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="N19" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="O19" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P19" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B20" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C20" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D20" t="s">
         <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="H20" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="I20" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="J20" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="K20" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="L20" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="M20" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="N20" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="O20" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="P20" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B21" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D21" t="s">
         <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H21" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I21" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="J21" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="K21" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="L21" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="Q21" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="B22" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D22" t="s">
         <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
       </c>
       <c r="G22" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H22" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I22" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="J22" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="K22" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="L22" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B23" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D23" t="s">
         <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
       </c>
       <c r="G23" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H23" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I23" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="J23" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="K23" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="L23" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="N23" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B24" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C24" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D24" t="s">
         <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="F24" t="s">
         <v>13</v>
       </c>
       <c r="G24" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H24" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="I24" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="J24" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="K24" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="L24" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="M24" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="N24" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="O24" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="P24" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D25" t="s">
         <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H25" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="I25" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="J25" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="K25" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="L25" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="M25" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="N25" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="O25" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="P25" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D26" t="s">
         <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
       </c>
       <c r="G26" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H26" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I26" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="J26" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="K26" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="L26" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C27" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D27" t="s">
         <v>34</v>
       </c>
       <c r="E27" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
       </c>
       <c r="G27" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H27" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I27" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="J27" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="K27" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="L27" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="N27" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B28" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C28" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D28" t="s">
         <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
       </c>
       <c r="G28" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H28" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I28" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="J28" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="K28" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="L28" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C29" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D29" t="s">
         <v>34</v>
       </c>
       <c r="E29" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
       </c>
       <c r="G29" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H29" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I29" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="J29" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="K29" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="L29" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="N29" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="B30" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C30" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D30" t="s">
         <v>34</v>
       </c>
       <c r="E30" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
       </c>
       <c r="G30" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H30" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I30" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="J30" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="K30" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="L30" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="B31" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D31" t="s">
         <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="F31" t="s">
         <v>13</v>
       </c>
       <c r="G31" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H31" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I31" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="J31" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="K31" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="L31" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="N31" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D32" t="s">
         <v>34</v>
       </c>
       <c r="E32" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H32" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I32" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="J32" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="K32" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="L32" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="N32" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="B33" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D33" t="s">
         <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F33" t="s">
         <v>13</v>
       </c>
       <c r="G33" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H33" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I33" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="J33" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="K33" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="L33" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="N33" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="Q33" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D34" t="s">
         <v>34</v>
       </c>
       <c r="E34" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F34" t="s">
         <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H34" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="I34" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="J34" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="K34" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="L34" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="P34" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C35" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D35" t="s">
         <v>34</v>
       </c>
       <c r="E35" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="F35" t="s">
         <v>13</v>
       </c>
       <c r="G35" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H35" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="I35" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="J35" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="K35" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="L35" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="O35" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="P35" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C36" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="D36" t="s">
         <v>34</v>
       </c>
       <c r="E36" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="F36" t="s">
         <v>13</v>
       </c>
       <c r="G36" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="H36" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="I36" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="J36" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="K36" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="M36" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="R36" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="S36" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B37" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C37" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="D37" t="s">
         <v>34</v>
       </c>
       <c r="E37" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="F37" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="G37" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="H37" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="I37" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="J37" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="L37" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="M37" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="R37" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="S37" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C38" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="D38" t="s">
         <v>34</v>
       </c>
       <c r="E38" t="s">
+        <v>330</v>
+      </c>
+      <c r="G38" t="s">
+        <v>331</v>
+      </c>
+      <c r="H38" t="s">
+        <v>332</v>
+      </c>
+      <c r="I38" t="s">
+        <v>137</v>
+      </c>
+      <c r="J38" t="s">
+        <v>329</v>
+      </c>
+      <c r="K38" t="s">
+        <v>333</v>
+      </c>
+      <c r="L38" t="s">
+        <v>334</v>
+      </c>
+      <c r="M38" t="s">
+        <v>335</v>
+      </c>
+      <c r="R38" t="s">
+        <v>336</v>
+      </c>
+      <c r="S38" t="s">
         <v>322</v>
-      </c>
-      <c r="G38" t="s">
-        <v>323</v>
-      </c>
-      <c r="H38" t="s">
-        <v>324</v>
-      </c>
-      <c r="I38" t="s">
-        <v>129</v>
-      </c>
-      <c r="J38" t="s">
-        <v>321</v>
-      </c>
-      <c r="K38" t="s">
-        <v>325</v>
-      </c>
-      <c r="L38" t="s">
-        <v>326</v>
-      </c>
-      <c r="M38" t="s">
-        <v>327</v>
-      </c>
-      <c r="R38" t="s">
-        <v>328</v>
-      </c>
-      <c r="S38" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="B39" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C39" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="D39" t="s">
         <v>34</v>
       </c>
       <c r="E39" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="F39" t="s">
         <v>13</v>
       </c>
       <c r="G39" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="H39" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="I39" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="J39" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="K39" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="L39" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="M39" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="R39" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="S39" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -3916,46 +3981,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="B2" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C2" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B3" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C3" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="B4" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="C4" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B5" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C5" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>

--- a/ro-crate/ro-crate-metadata.xlsx
+++ b/ro-crate/ro-crate-metadata.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="351">
   <si>
     <t>Name</t>
   </si>
@@ -575,7 +575,7 @@
     <t>https://raw.githubusercontent.com/Australian-Text-Analytics-Platform/discursis/master/docs/Discursis%20User%20Guide.pdf</t>
   </si>
   <si>
-    <t>object Object</t>
+    <t>Based on Angus, D., Smith, A. E., &amp; Wiles, J. (2012). Human Communication as Coupled Time Series: Quantifying Multi-Participant Recurrence. IEEE Transactions on Audio, Speech, and Language Processing, 20(6), 1795–1807. https://doi.org/10.1109/TASL.2012.2189566</t>
   </si>
   <si>
     <t>arcp://name,DocumentSimilarity</t>
@@ -769,6 +769,9 @@
   </si>
   <si>
     <t>https://www.elararchive.org/uncategorized/SO_7557c4dd-1c83-485c-b95c-c0a292cfc42c/</t>
+  </si>
+  <si>
+    <t>object Object</t>
   </si>
   <si>
     <t>arcp://name,NetworkVisualiser</t>
@@ -3145,12 +3148,12 @@
         <v>249</v>
       </c>
       <c r="P20" t="s">
-        <v>185</v>
+        <v>250</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B21" t="s">
         <v>132</v>
@@ -3162,7 +3165,7 @@
         <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
@@ -3180,18 +3183,18 @@
         <v>146</v>
       </c>
       <c r="K21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L21" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q21" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B22" t="s">
         <v>132</v>
@@ -3203,7 +3206,7 @@
         <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
@@ -3221,7 +3224,7 @@
         <v>146</v>
       </c>
       <c r="K22" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L22" t="s">
         <v>148</v>
@@ -3229,7 +3232,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B23" t="s">
         <v>132</v>
@@ -3241,7 +3244,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
@@ -3259,18 +3262,18 @@
         <v>152</v>
       </c>
       <c r="K23" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L23" t="s">
         <v>148</v>
       </c>
       <c r="N23" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B24" t="s">
         <v>132</v>
@@ -3282,7 +3285,7 @@
         <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F24" t="s">
         <v>13</v>
@@ -3297,30 +3300,30 @@
         <v>137</v>
       </c>
       <c r="J24" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K24" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L24" t="s">
         <v>164</v>
       </c>
       <c r="M24" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N24" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O24" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P24" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B25" t="s">
         <v>132</v>
@@ -3332,7 +3335,7 @@
         <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
@@ -3347,30 +3350,30 @@
         <v>137</v>
       </c>
       <c r="J25" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K25" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L25" t="s">
         <v>164</v>
       </c>
       <c r="M25" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N25" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P25" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B26" t="s">
         <v>132</v>
@@ -3382,7 +3385,7 @@
         <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
@@ -3400,7 +3403,7 @@
         <v>146</v>
       </c>
       <c r="K26" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L26" t="s">
         <v>148</v>
@@ -3408,7 +3411,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B27" t="s">
         <v>132</v>
@@ -3420,7 +3423,7 @@
         <v>34</v>
       </c>
       <c r="E27" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
@@ -3438,18 +3441,18 @@
         <v>152</v>
       </c>
       <c r="K27" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L27" t="s">
         <v>148</v>
       </c>
       <c r="N27" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B28" t="s">
         <v>132</v>
@@ -3461,7 +3464,7 @@
         <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
@@ -3479,7 +3482,7 @@
         <v>146</v>
       </c>
       <c r="K28" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L28" t="s">
         <v>148</v>
@@ -3487,7 +3490,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B29" t="s">
         <v>132</v>
@@ -3499,7 +3502,7 @@
         <v>34</v>
       </c>
       <c r="E29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
@@ -3517,18 +3520,18 @@
         <v>152</v>
       </c>
       <c r="K29" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L29" t="s">
         <v>148</v>
       </c>
       <c r="N29" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B30" t="s">
         <v>132</v>
@@ -3540,7 +3543,7 @@
         <v>34</v>
       </c>
       <c r="E30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
@@ -3558,7 +3561,7 @@
         <v>146</v>
       </c>
       <c r="K30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L30" t="s">
         <v>148</v>
@@ -3566,7 +3569,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B31" t="s">
         <v>132</v>
@@ -3578,7 +3581,7 @@
         <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F31" t="s">
         <v>13</v>
@@ -3596,18 +3599,18 @@
         <v>152</v>
       </c>
       <c r="K31" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L31" t="s">
         <v>148</v>
       </c>
       <c r="N31" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s">
         <v>132</v>
@@ -3619,7 +3622,7 @@
         <v>34</v>
       </c>
       <c r="E32" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
@@ -3637,18 +3640,18 @@
         <v>152</v>
       </c>
       <c r="K32" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L32" t="s">
         <v>148</v>
       </c>
       <c r="N32" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B33" t="s">
         <v>132</v>
@@ -3660,7 +3663,7 @@
         <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F33" t="s">
         <v>13</v>
@@ -3678,21 +3681,21 @@
         <v>152</v>
       </c>
       <c r="K33" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L33" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N33" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q33" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B34" t="s">
         <v>132</v>
@@ -3704,7 +3707,7 @@
         <v>34</v>
       </c>
       <c r="E34" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F34" t="s">
         <v>13</v>
@@ -3713,27 +3716,27 @@
         <v>160</v>
       </c>
       <c r="H34" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I34" t="s">
         <v>137</v>
       </c>
       <c r="J34" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K34" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L34" t="s">
         <v>164</v>
       </c>
       <c r="P34" t="s">
-        <v>185</v>
+        <v>250</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B35" t="s">
         <v>132</v>
@@ -3745,7 +3748,7 @@
         <v>34</v>
       </c>
       <c r="E35" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F35" t="s">
         <v>13</v>
@@ -3760,36 +3763,36 @@
         <v>137</v>
       </c>
       <c r="J35" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K35" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L35" t="s">
         <v>164</v>
       </c>
       <c r="O35" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P35" t="s">
-        <v>185</v>
+        <v>250</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B36" t="s">
         <v>132</v>
       </c>
       <c r="C36" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D36" t="s">
         <v>34</v>
       </c>
       <c r="E36" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F36" t="s">
         <v>13</v>
@@ -3798,160 +3801,160 @@
         <v>135</v>
       </c>
       <c r="H36" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I36" t="s">
         <v>137</v>
       </c>
       <c r="J36" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K36" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="R36" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="S36" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B37" t="s">
         <v>132</v>
       </c>
       <c r="C37" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D37" t="s">
         <v>34</v>
       </c>
       <c r="E37" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F37" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G37" t="s">
         <v>135</v>
       </c>
       <c r="H37" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I37" t="s">
         <v>137</v>
       </c>
       <c r="J37" t="s">
+        <v>324</v>
+      </c>
+      <c r="L37" t="s">
+        <v>328</v>
+      </c>
+      <c r="M37" t="s">
+        <v>324</v>
+      </c>
+      <c r="R37" t="s">
+        <v>329</v>
+      </c>
+      <c r="S37" t="s">
         <v>323</v>
-      </c>
-      <c r="L37" t="s">
-        <v>327</v>
-      </c>
-      <c r="M37" t="s">
-        <v>323</v>
-      </c>
-      <c r="R37" t="s">
-        <v>328</v>
-      </c>
-      <c r="S37" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B38" t="s">
         <v>132</v>
       </c>
       <c r="C38" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D38" t="s">
         <v>34</v>
       </c>
       <c r="E38" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G38" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H38" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="I38" t="s">
         <v>137</v>
       </c>
       <c r="J38" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K38" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L38" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M38" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="R38" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="S38" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B39" t="s">
         <v>132</v>
       </c>
       <c r="C39" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D39" t="s">
         <v>34</v>
       </c>
       <c r="E39" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F39" t="s">
         <v>13</v>
       </c>
       <c r="G39" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H39" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="I39" t="s">
         <v>137</v>
       </c>
       <c r="J39" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K39" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L39" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M39" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="R39" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="S39" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -3981,46 +3984,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C3" t="s">
         <v>345</v>
-      </c>
-      <c r="B3" t="s">
-        <v>346</v>
-      </c>
-      <c r="C3" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B4" t="s">
-        <v>185</v>
+        <v>250</v>
       </c>
       <c r="C4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>

--- a/ro-crate/ro-crate-metadata.xlsx
+++ b/ro-crate/ro-crate-metadata.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="350">
   <si>
     <t>Name</t>
   </si>
@@ -347,7 +347,7 @@
     <t>https://github.com/SLCLADAL/ladal</t>
   </si>
   <si>
-    <t>Language Technology and Data Analysis Laboratory</t>
+    <t>Language Technology and Data Analysis Laboratory (LADAL)</t>
   </si>
   <si>
     <t>https://hass.uq.edu.au/centre-digital-cultures-societies</t>
@@ -575,7 +575,7 @@
     <t>https://raw.githubusercontent.com/Australian-Text-Analytics-Platform/discursis/master/docs/Discursis%20User%20Guide.pdf</t>
   </si>
   <si>
-    <t>Based on Angus, D., Smith, A. E., &amp; Wiles, J. (2012). Human Communication as Coupled Time Series: Quantifying Multi-Participant Recurrence. IEEE Transactions on Audio, Speech, and Language Processing, 20(6), 1795–1807. https://doi.org/10.1109/TASL.2012.2189566</t>
+    <t>object Object</t>
   </si>
   <si>
     <t>arcp://name,DocumentSimilarity</t>
@@ -769,9 +769,6 @@
   </si>
   <si>
     <t>https://www.elararchive.org/uncategorized/SO_7557c4dd-1c83-485c-b95c-c0a292cfc42c/</t>
-  </si>
-  <si>
-    <t>object Object</t>
   </si>
   <si>
     <t>arcp://name,NetworkVisualiser</t>
@@ -2638,7 +2635,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>186</v>
       </c>
@@ -2686,6 +2683,9 @@
       </c>
       <c r="P9" t="s">
         <v>193</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -3051,7 +3051,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>233</v>
       </c>
@@ -3099,6 +3099,9 @@
       </c>
       <c r="P19" t="s">
         <v>239</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -3148,12 +3151,12 @@
         <v>249</v>
       </c>
       <c r="P20" t="s">
-        <v>250</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B21" t="s">
         <v>132</v>
@@ -3165,7 +3168,7 @@
         <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
@@ -3183,18 +3186,18 @@
         <v>146</v>
       </c>
       <c r="K21" t="s">
+        <v>252</v>
+      </c>
+      <c r="L21" t="s">
         <v>253</v>
       </c>
-      <c r="L21" t="s">
+      <c r="Q21" t="s">
         <v>254</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B22" t="s">
         <v>132</v>
@@ -3206,7 +3209,7 @@
         <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
@@ -3224,7 +3227,7 @@
         <v>146</v>
       </c>
       <c r="K22" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L22" t="s">
         <v>148</v>
@@ -3232,7 +3235,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B23" t="s">
         <v>132</v>
@@ -3244,7 +3247,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
@@ -3262,18 +3265,18 @@
         <v>152</v>
       </c>
       <c r="K23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L23" t="s">
         <v>148</v>
       </c>
       <c r="N23" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>262</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>263</v>
       </c>
       <c r="B24" t="s">
         <v>132</v>
@@ -3285,7 +3288,7 @@
         <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F24" t="s">
         <v>13</v>
@@ -3300,30 +3303,33 @@
         <v>137</v>
       </c>
       <c r="J24" t="s">
+        <v>264</v>
+      </c>
+      <c r="K24" t="s">
         <v>265</v>
-      </c>
-      <c r="K24" t="s">
-        <v>266</v>
       </c>
       <c r="L24" t="s">
         <v>164</v>
       </c>
       <c r="M24" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N24" t="s">
+        <v>266</v>
+      </c>
+      <c r="O24" t="s">
         <v>267</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>268</v>
       </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>269</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>270</v>
       </c>
       <c r="B25" t="s">
         <v>132</v>
@@ -3335,7 +3341,7 @@
         <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
@@ -3350,30 +3356,33 @@
         <v>137</v>
       </c>
       <c r="J25" t="s">
+        <v>271</v>
+      </c>
+      <c r="K25" t="s">
         <v>272</v>
-      </c>
-      <c r="K25" t="s">
-        <v>273</v>
       </c>
       <c r="L25" t="s">
         <v>164</v>
       </c>
       <c r="M25" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N25" t="s">
+        <v>273</v>
+      </c>
+      <c r="O25" t="s">
         <v>274</v>
       </c>
-      <c r="O25" t="s">
+      <c r="P25" t="s">
         <v>275</v>
       </c>
-      <c r="P25" t="s">
-        <v>276</v>
+      <c r="Q25" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B26" t="s">
         <v>132</v>
@@ -3385,7 +3394,7 @@
         <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
@@ -3403,7 +3412,7 @@
         <v>146</v>
       </c>
       <c r="K26" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L26" t="s">
         <v>148</v>
@@ -3411,7 +3420,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B27" t="s">
         <v>132</v>
@@ -3423,7 +3432,7 @@
         <v>34</v>
       </c>
       <c r="E27" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
@@ -3441,18 +3450,18 @@
         <v>152</v>
       </c>
       <c r="K27" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L27" t="s">
         <v>148</v>
       </c>
       <c r="N27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B28" t="s">
         <v>132</v>
@@ -3464,7 +3473,7 @@
         <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
@@ -3482,7 +3491,7 @@
         <v>146</v>
       </c>
       <c r="K28" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L28" t="s">
         <v>148</v>
@@ -3490,7 +3499,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s">
         <v>132</v>
@@ -3502,7 +3511,7 @@
         <v>34</v>
       </c>
       <c r="E29" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
@@ -3520,18 +3529,18 @@
         <v>152</v>
       </c>
       <c r="K29" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L29" t="s">
         <v>148</v>
       </c>
       <c r="N29" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B30" t="s">
         <v>132</v>
@@ -3543,7 +3552,7 @@
         <v>34</v>
       </c>
       <c r="E30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
@@ -3561,7 +3570,7 @@
         <v>146</v>
       </c>
       <c r="K30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L30" t="s">
         <v>148</v>
@@ -3569,7 +3578,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B31" t="s">
         <v>132</v>
@@ -3581,7 +3590,7 @@
         <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F31" t="s">
         <v>13</v>
@@ -3599,18 +3608,18 @@
         <v>152</v>
       </c>
       <c r="K31" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L31" t="s">
         <v>148</v>
       </c>
       <c r="N31" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s">
         <v>132</v>
@@ -3622,7 +3631,7 @@
         <v>34</v>
       </c>
       <c r="E32" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
@@ -3640,18 +3649,18 @@
         <v>152</v>
       </c>
       <c r="K32" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L32" t="s">
         <v>148</v>
       </c>
       <c r="N32" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B33" t="s">
         <v>132</v>
@@ -3663,7 +3672,7 @@
         <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F33" t="s">
         <v>13</v>
@@ -3681,21 +3690,21 @@
         <v>152</v>
       </c>
       <c r="K33" t="s">
+        <v>303</v>
+      </c>
+      <c r="L33" t="s">
+        <v>253</v>
+      </c>
+      <c r="N33" t="s">
         <v>304</v>
       </c>
-      <c r="L33" t="s">
+      <c r="Q33" t="s">
         <v>254</v>
-      </c>
-      <c r="N33" t="s">
-        <v>305</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s">
         <v>132</v>
@@ -3707,7 +3716,7 @@
         <v>34</v>
       </c>
       <c r="E34" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F34" t="s">
         <v>13</v>
@@ -3716,27 +3725,27 @@
         <v>160</v>
       </c>
       <c r="H34" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="I34" t="s">
         <v>137</v>
       </c>
       <c r="J34" t="s">
+        <v>308</v>
+      </c>
+      <c r="K34" t="s">
         <v>309</v>
-      </c>
-      <c r="K34" t="s">
-        <v>310</v>
       </c>
       <c r="L34" t="s">
         <v>164</v>
       </c>
       <c r="P34" t="s">
-        <v>250</v>
+        <v>185</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s">
         <v>132</v>
@@ -3748,7 +3757,7 @@
         <v>34</v>
       </c>
       <c r="E35" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F35" t="s">
         <v>13</v>
@@ -3763,36 +3772,36 @@
         <v>137</v>
       </c>
       <c r="J35" t="s">
+        <v>312</v>
+      </c>
+      <c r="K35" t="s">
         <v>313</v>
-      </c>
-      <c r="K35" t="s">
-        <v>314</v>
       </c>
       <c r="L35" t="s">
         <v>164</v>
       </c>
       <c r="O35" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P35" t="s">
-        <v>250</v>
+        <v>185</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s">
         <v>132</v>
       </c>
       <c r="C36" t="s">
+        <v>316</v>
+      </c>
+      <c r="D36" t="s">
+        <v>34</v>
+      </c>
+      <c r="E36" t="s">
         <v>317</v>
-      </c>
-      <c r="D36" t="s">
-        <v>34</v>
-      </c>
-      <c r="E36" t="s">
-        <v>318</v>
       </c>
       <c r="F36" t="s">
         <v>13</v>
@@ -3801,160 +3810,160 @@
         <v>135</v>
       </c>
       <c r="H36" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I36" t="s">
         <v>137</v>
       </c>
       <c r="J36" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K36" t="s">
+        <v>319</v>
+      </c>
+      <c r="M36" t="s">
         <v>320</v>
       </c>
-      <c r="M36" t="s">
+      <c r="R36" t="s">
         <v>321</v>
       </c>
-      <c r="R36" t="s">
+      <c r="S36" t="s">
         <v>322</v>
-      </c>
-      <c r="S36" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B37" t="s">
         <v>132</v>
       </c>
       <c r="C37" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D37" t="s">
         <v>34</v>
       </c>
       <c r="E37" t="s">
+        <v>324</v>
+      </c>
+      <c r="F37" t="s">
         <v>325</v>
-      </c>
-      <c r="F37" t="s">
-        <v>326</v>
       </c>
       <c r="G37" t="s">
         <v>135</v>
       </c>
       <c r="H37" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I37" t="s">
         <v>137</v>
       </c>
       <c r="J37" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L37" t="s">
+        <v>327</v>
+      </c>
+      <c r="M37" t="s">
+        <v>323</v>
+      </c>
+      <c r="R37" t="s">
         <v>328</v>
       </c>
-      <c r="M37" t="s">
-        <v>324</v>
-      </c>
-      <c r="R37" t="s">
-        <v>329</v>
-      </c>
       <c r="S37" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B38" t="s">
         <v>132</v>
       </c>
       <c r="C38" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D38" t="s">
         <v>34</v>
       </c>
       <c r="E38" t="s">
+        <v>330</v>
+      </c>
+      <c r="G38" t="s">
         <v>331</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
         <v>332</v>
-      </c>
-      <c r="H38" t="s">
-        <v>333</v>
       </c>
       <c r="I38" t="s">
         <v>137</v>
       </c>
       <c r="J38" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="K38" t="s">
+        <v>333</v>
+      </c>
+      <c r="L38" t="s">
         <v>334</v>
       </c>
-      <c r="L38" t="s">
+      <c r="M38" t="s">
         <v>335</v>
       </c>
-      <c r="M38" t="s">
+      <c r="R38" t="s">
         <v>336</v>
       </c>
-      <c r="R38" t="s">
-        <v>337</v>
-      </c>
       <c r="S38" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B39" t="s">
         <v>132</v>
       </c>
       <c r="C39" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D39" t="s">
         <v>34</v>
       </c>
       <c r="E39" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F39" t="s">
         <v>13</v>
       </c>
       <c r="G39" t="s">
+        <v>331</v>
+      </c>
+      <c r="H39" t="s">
         <v>332</v>
-      </c>
-      <c r="H39" t="s">
-        <v>333</v>
       </c>
       <c r="I39" t="s">
         <v>137</v>
       </c>
       <c r="J39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K39" t="s">
+        <v>339</v>
+      </c>
+      <c r="L39" t="s">
+        <v>334</v>
+      </c>
+      <c r="M39" t="s">
         <v>340</v>
       </c>
-      <c r="L39" t="s">
-        <v>335</v>
-      </c>
-      <c r="M39" t="s">
+      <c r="R39" t="s">
         <v>341</v>
       </c>
-      <c r="R39" t="s">
-        <v>342</v>
-      </c>
       <c r="S39" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -3984,46 +3993,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B2" t="s">
         <v>343</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>344</v>
-      </c>
-      <c r="C2" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B3" t="s">
         <v>346</v>
       </c>
-      <c r="B3" t="s">
-        <v>347</v>
-      </c>
       <c r="C3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B4" t="s">
-        <v>250</v>
+        <v>185</v>
       </c>
       <c r="C4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>348</v>
+      </c>
+      <c r="B5" t="s">
         <v>349</v>
       </c>
-      <c r="B5" t="s">
-        <v>350</v>
-      </c>
       <c r="C5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>

--- a/ro-crate/ro-crate-metadata.xlsx
+++ b/ro-crate/ro-crate-metadata.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="351">
   <si>
     <t>Name</t>
   </si>
@@ -600,6 +600,9 @@
   </si>
   <si>
     <t>Jufri, Sony &amp; Sun, Chao (2024). Document Similarity. v1.2. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/document-similarity</t>
+  </si>
+  <si>
+    <t>Read more about the Document Similarity tool on the LDaCA blog.</t>
   </si>
   <si>
     <t>arcp://name,ELANAnnotationSplitter</t>
@@ -2685,12 +2688,12 @@
         <v>193</v>
       </c>
       <c r="Q9" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B10" t="s">
         <v>132</v>
@@ -2702,7 +2705,7 @@
         <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
@@ -2714,24 +2717,24 @@
         <v>136</v>
       </c>
       <c r="I10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L10" t="s">
         <v>140</v>
       </c>
       <c r="M10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B11" t="s">
         <v>132</v>
@@ -2743,7 +2746,7 @@
         <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
@@ -2755,24 +2758,24 @@
         <v>136</v>
       </c>
       <c r="I11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B12" t="s">
         <v>132</v>
@@ -2784,7 +2787,7 @@
         <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
@@ -2799,10 +2802,10 @@
         <v>151</v>
       </c>
       <c r="J12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L12" t="s">
         <v>140</v>
@@ -2810,7 +2813,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B13" t="s">
         <v>132</v>
@@ -2822,7 +2825,7 @@
         <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
@@ -2837,10 +2840,10 @@
         <v>151</v>
       </c>
       <c r="J13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L13" t="s">
         <v>140</v>
@@ -2848,7 +2851,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B14" t="s">
         <v>132</v>
@@ -2860,7 +2863,7 @@
         <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
@@ -2872,24 +2875,24 @@
         <v>136</v>
       </c>
       <c r="I14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L14" t="s">
         <v>140</v>
       </c>
       <c r="M14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B15" t="s">
         <v>132</v>
@@ -2901,7 +2904,7 @@
         <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
@@ -2919,18 +2922,18 @@
         <v>152</v>
       </c>
       <c r="K15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L15" t="s">
         <v>148</v>
       </c>
       <c r="N15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B16" t="s">
         <v>132</v>
@@ -2942,39 +2945,39 @@
         <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I16" t="s">
         <v>137</v>
       </c>
       <c r="J16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K16" t="s">
+        <v>224</v>
+      </c>
+      <c r="L16" t="s">
+        <v>225</v>
+      </c>
+      <c r="M16" t="s">
         <v>223</v>
       </c>
-      <c r="L16" t="s">
-        <v>224</v>
-      </c>
-      <c r="M16" t="s">
-        <v>222</v>
-      </c>
       <c r="N16" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B17" t="s">
         <v>132</v>
@@ -2986,7 +2989,7 @@
         <v>34</v>
       </c>
       <c r="E17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
@@ -3004,7 +3007,7 @@
         <v>146</v>
       </c>
       <c r="K17" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L17" t="s">
         <v>148</v>
@@ -3012,7 +3015,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B18" t="s">
         <v>132</v>
@@ -3024,7 +3027,7 @@
         <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
@@ -3042,18 +3045,18 @@
         <v>152</v>
       </c>
       <c r="K18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L18" t="s">
         <v>148</v>
       </c>
       <c r="N18" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B19" t="s">
         <v>132</v>
@@ -3065,7 +3068,7 @@
         <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
@@ -3080,25 +3083,25 @@
         <v>137</v>
       </c>
       <c r="J19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K19" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L19" t="s">
         <v>164</v>
       </c>
       <c r="M19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N19" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O19" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P19" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q19" t="s">
         <v>185</v>
@@ -3106,7 +3109,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B20" t="s">
         <v>132</v>
@@ -3118,37 +3121,37 @@
         <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H20" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L20" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M20" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N20" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O20" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P20" t="s">
         <v>185</v>
@@ -3156,7 +3159,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B21" t="s">
         <v>132</v>
@@ -3168,7 +3171,7 @@
         <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
@@ -3186,18 +3189,18 @@
         <v>146</v>
       </c>
       <c r="K21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L21" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q21" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B22" t="s">
         <v>132</v>
@@ -3209,7 +3212,7 @@
         <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
@@ -3227,7 +3230,7 @@
         <v>146</v>
       </c>
       <c r="K22" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L22" t="s">
         <v>148</v>
@@ -3235,7 +3238,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B23" t="s">
         <v>132</v>
@@ -3247,7 +3250,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
@@ -3265,18 +3268,18 @@
         <v>152</v>
       </c>
       <c r="K23" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L23" t="s">
         <v>148</v>
       </c>
       <c r="N23" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B24" t="s">
         <v>132</v>
@@ -3288,7 +3291,7 @@
         <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F24" t="s">
         <v>13</v>
@@ -3303,25 +3306,25 @@
         <v>137</v>
       </c>
       <c r="J24" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K24" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L24" t="s">
         <v>164</v>
       </c>
       <c r="M24" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N24" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O24" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P24" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q24" t="s">
         <v>185</v>
@@ -3329,7 +3332,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B25" t="s">
         <v>132</v>
@@ -3341,7 +3344,7 @@
         <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
@@ -3356,25 +3359,25 @@
         <v>137</v>
       </c>
       <c r="J25" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K25" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L25" t="s">
         <v>164</v>
       </c>
       <c r="M25" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N25" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P25" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q25" t="s">
         <v>185</v>
@@ -3382,7 +3385,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B26" t="s">
         <v>132</v>
@@ -3394,7 +3397,7 @@
         <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
@@ -3412,7 +3415,7 @@
         <v>146</v>
       </c>
       <c r="K26" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L26" t="s">
         <v>148</v>
@@ -3420,7 +3423,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B27" t="s">
         <v>132</v>
@@ -3432,7 +3435,7 @@
         <v>34</v>
       </c>
       <c r="E27" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
@@ -3450,18 +3453,18 @@
         <v>152</v>
       </c>
       <c r="K27" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L27" t="s">
         <v>148</v>
       </c>
       <c r="N27" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B28" t="s">
         <v>132</v>
@@ -3473,7 +3476,7 @@
         <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
@@ -3491,7 +3494,7 @@
         <v>146</v>
       </c>
       <c r="K28" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L28" t="s">
         <v>148</v>
@@ -3499,7 +3502,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B29" t="s">
         <v>132</v>
@@ -3511,7 +3514,7 @@
         <v>34</v>
       </c>
       <c r="E29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
@@ -3529,18 +3532,18 @@
         <v>152</v>
       </c>
       <c r="K29" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L29" t="s">
         <v>148</v>
       </c>
       <c r="N29" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B30" t="s">
         <v>132</v>
@@ -3552,7 +3555,7 @@
         <v>34</v>
       </c>
       <c r="E30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
@@ -3570,7 +3573,7 @@
         <v>146</v>
       </c>
       <c r="K30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L30" t="s">
         <v>148</v>
@@ -3578,7 +3581,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B31" t="s">
         <v>132</v>
@@ -3590,7 +3593,7 @@
         <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F31" t="s">
         <v>13</v>
@@ -3608,18 +3611,18 @@
         <v>152</v>
       </c>
       <c r="K31" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L31" t="s">
         <v>148</v>
       </c>
       <c r="N31" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s">
         <v>132</v>
@@ -3631,7 +3634,7 @@
         <v>34</v>
       </c>
       <c r="E32" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
@@ -3649,18 +3652,18 @@
         <v>152</v>
       </c>
       <c r="K32" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L32" t="s">
         <v>148</v>
       </c>
       <c r="N32" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B33" t="s">
         <v>132</v>
@@ -3672,7 +3675,7 @@
         <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F33" t="s">
         <v>13</v>
@@ -3690,21 +3693,21 @@
         <v>152</v>
       </c>
       <c r="K33" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L33" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N33" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q33" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B34" t="s">
         <v>132</v>
@@ -3716,7 +3719,7 @@
         <v>34</v>
       </c>
       <c r="E34" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F34" t="s">
         <v>13</v>
@@ -3725,16 +3728,16 @@
         <v>160</v>
       </c>
       <c r="H34" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I34" t="s">
         <v>137</v>
       </c>
       <c r="J34" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K34" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L34" t="s">
         <v>164</v>
@@ -3745,7 +3748,7 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B35" t="s">
         <v>132</v>
@@ -3757,7 +3760,7 @@
         <v>34</v>
       </c>
       <c r="E35" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F35" t="s">
         <v>13</v>
@@ -3772,16 +3775,16 @@
         <v>137</v>
       </c>
       <c r="J35" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K35" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L35" t="s">
         <v>164</v>
       </c>
       <c r="O35" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P35" t="s">
         <v>185</v>
@@ -3789,19 +3792,19 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B36" t="s">
         <v>132</v>
       </c>
       <c r="C36" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D36" t="s">
         <v>34</v>
       </c>
       <c r="E36" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F36" t="s">
         <v>13</v>
@@ -3810,160 +3813,160 @@
         <v>135</v>
       </c>
       <c r="H36" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I36" t="s">
         <v>137</v>
       </c>
       <c r="J36" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K36" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="R36" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="S36" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B37" t="s">
         <v>132</v>
       </c>
       <c r="C37" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D37" t="s">
         <v>34</v>
       </c>
       <c r="E37" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F37" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G37" t="s">
         <v>135</v>
       </c>
       <c r="H37" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I37" t="s">
         <v>137</v>
       </c>
       <c r="J37" t="s">
+        <v>324</v>
+      </c>
+      <c r="L37" t="s">
+        <v>328</v>
+      </c>
+      <c r="M37" t="s">
+        <v>324</v>
+      </c>
+      <c r="R37" t="s">
+        <v>329</v>
+      </c>
+      <c r="S37" t="s">
         <v>323</v>
-      </c>
-      <c r="L37" t="s">
-        <v>327</v>
-      </c>
-      <c r="M37" t="s">
-        <v>323</v>
-      </c>
-      <c r="R37" t="s">
-        <v>328</v>
-      </c>
-      <c r="S37" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B38" t="s">
         <v>132</v>
       </c>
       <c r="C38" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D38" t="s">
         <v>34</v>
       </c>
       <c r="E38" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G38" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H38" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="I38" t="s">
         <v>137</v>
       </c>
       <c r="J38" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K38" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L38" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M38" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="R38" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="S38" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B39" t="s">
         <v>132</v>
       </c>
       <c r="C39" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D39" t="s">
         <v>34</v>
       </c>
       <c r="E39" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F39" t="s">
         <v>13</v>
       </c>
       <c r="G39" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H39" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="I39" t="s">
         <v>137</v>
       </c>
       <c r="J39" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K39" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L39" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M39" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="R39" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="S39" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -3993,46 +3996,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C3" t="s">
         <v>345</v>
-      </c>
-      <c r="B3" t="s">
-        <v>346</v>
-      </c>
-      <c r="C3" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B4" t="s">
         <v>185</v>
       </c>
       <c r="C4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>

--- a/ro-crate/ro-crate-metadata.xlsx
+++ b/ro-crate/ro-crate-metadata.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="355">
   <si>
     <t>Name</t>
   </si>
@@ -741,6 +741,9 @@
   </si>
   <si>
     <t>Jufri, Sony &amp; Sun, Chao (2022). Keywords Analysis. v1.0. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/keywords-analysis</t>
+  </si>
+  <si>
+    <t>Read more about the Keyword Analysis tool on the LDaCA blog.</t>
   </si>
   <si>
     <t>arcp://name,Lameta</t>
@@ -831,6 +834,9 @@
     <t>Jufri, Sony &amp; Sun, Chao (2022). Quotation Tool. v1.0. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/quotation-tool</t>
   </si>
   <si>
+    <t>Read more about the Quotation Tool on the LDaCA blog.</t>
+  </si>
+  <si>
     <t>arcp://name,SemanticTaggerEnglish</t>
   </si>
   <si>
@@ -852,6 +858,9 @@
     <t>Jufri, Sony &amp; Sun, Chao (2022). Semantic Tagger. v1.0. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/semantic-tagger</t>
   </si>
   <si>
+    <t>Read more about the Semantic Tagger on the LDaCA blog.</t>
+  </si>
+  <si>
     <t>arcp://name,SentimentExplorer</t>
   </si>
   <si>
@@ -1066,6 +1075,9 @@
   </si>
   <si>
     <t>arcp://name,hdl10.25912~RDF_1754373503052</t>
+  </si>
+  <si>
+    <t>AusReddit aggregated data - Collection</t>
   </si>
   <si>
     <t>arcp://name,hdl10.25912~RDF_1758591652309</t>
@@ -3104,12 +3116,12 @@
         <v>240</v>
       </c>
       <c r="Q19" t="s">
-        <v>185</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B20" t="s">
         <v>132</v>
@@ -3121,37 +3133,37 @@
         <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I20" t="s">
         <v>197</v>
       </c>
       <c r="J20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K20" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L20" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M20" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N20" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O20" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P20" t="s">
         <v>185</v>
@@ -3159,7 +3171,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B21" t="s">
         <v>132</v>
@@ -3171,7 +3183,7 @@
         <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
@@ -3189,18 +3201,18 @@
         <v>146</v>
       </c>
       <c r="K21" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L21" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q21" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B22" t="s">
         <v>132</v>
@@ -3212,7 +3224,7 @@
         <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
@@ -3230,7 +3242,7 @@
         <v>146</v>
       </c>
       <c r="K22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L22" t="s">
         <v>148</v>
@@ -3238,7 +3250,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B23" t="s">
         <v>132</v>
@@ -3250,7 +3262,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
@@ -3268,18 +3280,18 @@
         <v>152</v>
       </c>
       <c r="K23" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L23" t="s">
         <v>148</v>
       </c>
       <c r="N23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B24" t="s">
         <v>132</v>
@@ -3291,7 +3303,7 @@
         <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F24" t="s">
         <v>13</v>
@@ -3306,33 +3318,33 @@
         <v>137</v>
       </c>
       <c r="J24" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K24" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L24" t="s">
         <v>164</v>
       </c>
       <c r="M24" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N24" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O24" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P24" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q24" t="s">
-        <v>185</v>
+        <v>271</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B25" t="s">
         <v>132</v>
@@ -3344,7 +3356,7 @@
         <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
@@ -3359,33 +3371,33 @@
         <v>137</v>
       </c>
       <c r="J25" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K25" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="L25" t="s">
         <v>164</v>
       </c>
       <c r="M25" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N25" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O25" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P25" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q25" t="s">
-        <v>185</v>
+        <v>279</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B26" t="s">
         <v>132</v>
@@ -3397,7 +3409,7 @@
         <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
@@ -3415,7 +3427,7 @@
         <v>146</v>
       </c>
       <c r="K26" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L26" t="s">
         <v>148</v>
@@ -3423,7 +3435,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B27" t="s">
         <v>132</v>
@@ -3435,7 +3447,7 @@
         <v>34</v>
       </c>
       <c r="E27" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
@@ -3453,18 +3465,18 @@
         <v>152</v>
       </c>
       <c r="K27" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="L27" t="s">
         <v>148</v>
       </c>
       <c r="N27" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B28" t="s">
         <v>132</v>
@@ -3476,7 +3488,7 @@
         <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
@@ -3494,7 +3506,7 @@
         <v>146</v>
       </c>
       <c r="K28" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="L28" t="s">
         <v>148</v>
@@ -3502,7 +3514,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B29" t="s">
         <v>132</v>
@@ -3514,7 +3526,7 @@
         <v>34</v>
       </c>
       <c r="E29" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
@@ -3532,18 +3544,18 @@
         <v>152</v>
       </c>
       <c r="K29" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="L29" t="s">
         <v>148</v>
       </c>
       <c r="N29" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B30" t="s">
         <v>132</v>
@@ -3555,7 +3567,7 @@
         <v>34</v>
       </c>
       <c r="E30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
@@ -3573,7 +3585,7 @@
         <v>146</v>
       </c>
       <c r="K30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L30" t="s">
         <v>148</v>
@@ -3581,7 +3593,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B31" t="s">
         <v>132</v>
@@ -3593,7 +3605,7 @@
         <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F31" t="s">
         <v>13</v>
@@ -3611,18 +3623,18 @@
         <v>152</v>
       </c>
       <c r="K31" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="L31" t="s">
         <v>148</v>
       </c>
       <c r="N31" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B32" t="s">
         <v>132</v>
@@ -3634,7 +3646,7 @@
         <v>34</v>
       </c>
       <c r="E32" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
@@ -3652,18 +3664,18 @@
         <v>152</v>
       </c>
       <c r="K32" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="L32" t="s">
         <v>148</v>
       </c>
       <c r="N32" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B33" t="s">
         <v>132</v>
@@ -3675,7 +3687,7 @@
         <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F33" t="s">
         <v>13</v>
@@ -3693,21 +3705,21 @@
         <v>152</v>
       </c>
       <c r="K33" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="L33" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N33" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q33" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B34" t="s">
         <v>132</v>
@@ -3719,7 +3731,7 @@
         <v>34</v>
       </c>
       <c r="E34" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="F34" t="s">
         <v>13</v>
@@ -3728,16 +3740,16 @@
         <v>160</v>
       </c>
       <c r="H34" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="I34" t="s">
         <v>137</v>
       </c>
       <c r="J34" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="K34" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="L34" t="s">
         <v>164</v>
@@ -3748,7 +3760,7 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B35" t="s">
         <v>132</v>
@@ -3760,7 +3772,7 @@
         <v>34</v>
       </c>
       <c r="E35" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F35" t="s">
         <v>13</v>
@@ -3775,16 +3787,16 @@
         <v>137</v>
       </c>
       <c r="J35" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="K35" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="L35" t="s">
         <v>164</v>
       </c>
       <c r="O35" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="P35" t="s">
         <v>185</v>
@@ -3792,19 +3804,19 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B36" t="s">
         <v>132</v>
       </c>
       <c r="C36" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D36" t="s">
         <v>34</v>
       </c>
       <c r="E36" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F36" t="s">
         <v>13</v>
@@ -3813,160 +3825,160 @@
         <v>135</v>
       </c>
       <c r="H36" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="I36" t="s">
         <v>137</v>
       </c>
       <c r="J36" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K36" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="M36" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="R36" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="S36" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s">
         <v>132</v>
       </c>
       <c r="C37" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D37" t="s">
         <v>34</v>
       </c>
       <c r="E37" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F37" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G37" t="s">
         <v>135</v>
       </c>
       <c r="H37" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="I37" t="s">
         <v>137</v>
       </c>
       <c r="J37" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="L37" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M37" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="R37" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="S37" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B38" t="s">
         <v>132</v>
       </c>
       <c r="C38" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D38" t="s">
         <v>34</v>
       </c>
       <c r="E38" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G38" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H38" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="I38" t="s">
         <v>137</v>
       </c>
       <c r="J38" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K38" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L38" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M38" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="R38" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="S38" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B39" t="s">
         <v>132</v>
       </c>
       <c r="C39" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D39" t="s">
         <v>34</v>
       </c>
       <c r="E39" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F39" t="s">
         <v>13</v>
       </c>
       <c r="G39" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H39" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="I39" t="s">
         <v>137</v>
       </c>
       <c r="J39" t="s">
+        <v>341</v>
+      </c>
+      <c r="K39" t="s">
+        <v>343</v>
+      </c>
+      <c r="L39" t="s">
         <v>338</v>
       </c>
-      <c r="K39" t="s">
-        <v>340</v>
-      </c>
-      <c r="L39" t="s">
-        <v>335</v>
-      </c>
       <c r="M39" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="R39" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="S39" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -3996,46 +4008,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B3" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C3" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C4" t="s">
         <v>348</v>
-      </c>
-      <c r="B4" t="s">
-        <v>185</v>
-      </c>
-      <c r="C4" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C5" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>

--- a/ro-crate/ro-crate-metadata.xlsx
+++ b/ro-crate/ro-crate-metadata.xlsx
@@ -981,7 +981,7 @@
     <t>https://data.ldaca.edu.au/object?_id=https://github.com/Australian-Text-Analytics-Platform/cooee/blob/main/cooee.ipynb</t>
   </si>
   <si>
-    <t>["https://w3id.org/ldac/profile#SoftwareTool", "object Object"]</t>
+    <t>["https://w3id.org/ldac/profile#SoftwareTool", "https://w3id.org/ldac/profile#Notebook"]</t>
   </si>
   <si>
     <t>COOEE Notebook</t>

--- a/ro-crate/ro-crate-metadata.xlsx
+++ b/ro-crate/ro-crate-metadata.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="351">
   <si>
     <t>Name</t>
   </si>
@@ -602,9 +602,6 @@
     <t>Jufri, Sony &amp; Sun, Chao (2024). Document Similarity. v1.2. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/document-similarity</t>
   </si>
   <si>
-    <t>Read more about the Document Similarity tool on the LDaCA blog.</t>
-  </si>
-  <si>
     <t>arcp://name,ELANAnnotationSplitter</t>
   </si>
   <si>
@@ -741,9 +738,6 @@
   </si>
   <si>
     <t>Jufri, Sony &amp; Sun, Chao (2022). Keywords Analysis. v1.0. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/keywords-analysis</t>
-  </si>
-  <si>
-    <t>Read more about the Keyword Analysis tool on the LDaCA blog.</t>
   </si>
   <si>
     <t>arcp://name,Lameta</t>
@@ -834,9 +828,6 @@
     <t>Jufri, Sony &amp; Sun, Chao (2022). Quotation Tool. v1.0. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/quotation-tool</t>
   </si>
   <si>
-    <t>Read more about the Quotation Tool on the LDaCA blog.</t>
-  </si>
-  <si>
     <t>arcp://name,SemanticTaggerEnglish</t>
   </si>
   <si>
@@ -856,9 +847,6 @@
   </si>
   <si>
     <t>Jufri, Sony &amp; Sun, Chao (2022). Semantic Tagger. v1.0. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/semantic-tagger</t>
-  </si>
-  <si>
-    <t>Read more about the Semantic Tagger on the LDaCA blog.</t>
   </si>
   <si>
     <t>arcp://name,SentimentExplorer</t>
@@ -2650,7 +2638,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>186</v>
       </c>
@@ -2699,13 +2687,10 @@
       <c r="P9" t="s">
         <v>193</v>
       </c>
-      <c r="Q9" t="s">
-        <v>194</v>
-      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" t="s">
         <v>132</v>
@@ -2717,7 +2702,7 @@
         <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
@@ -2729,24 +2714,24 @@
         <v>136</v>
       </c>
       <c r="I10" t="s">
+        <v>196</v>
+      </c>
+      <c r="J10" t="s">
         <v>197</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>198</v>
-      </c>
-      <c r="K10" t="s">
-        <v>199</v>
       </c>
       <c r="L10" t="s">
         <v>140</v>
       </c>
       <c r="M10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B11" t="s">
         <v>132</v>
@@ -2758,7 +2743,7 @@
         <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
@@ -2770,24 +2755,24 @@
         <v>136</v>
       </c>
       <c r="I11" t="s">
+        <v>196</v>
+      </c>
+      <c r="J11" t="s">
         <v>197</v>
       </c>
-      <c r="J11" t="s">
-        <v>198</v>
-      </c>
       <c r="K11" t="s">
+        <v>201</v>
+      </c>
+      <c r="L11" t="s">
         <v>202</v>
       </c>
-      <c r="L11" t="s">
-        <v>203</v>
-      </c>
       <c r="M11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B12" t="s">
         <v>132</v>
@@ -2799,7 +2784,7 @@
         <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
@@ -2814,10 +2799,10 @@
         <v>151</v>
       </c>
       <c r="J12" t="s">
+        <v>205</v>
+      </c>
+      <c r="K12" t="s">
         <v>206</v>
-      </c>
-      <c r="K12" t="s">
-        <v>207</v>
       </c>
       <c r="L12" t="s">
         <v>140</v>
@@ -2825,7 +2810,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B13" t="s">
         <v>132</v>
@@ -2837,7 +2822,7 @@
         <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
@@ -2852,10 +2837,10 @@
         <v>151</v>
       </c>
       <c r="J13" t="s">
+        <v>209</v>
+      </c>
+      <c r="K13" t="s">
         <v>210</v>
-      </c>
-      <c r="K13" t="s">
-        <v>211</v>
       </c>
       <c r="L13" t="s">
         <v>140</v>
@@ -2863,7 +2848,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B14" t="s">
         <v>132</v>
@@ -2875,7 +2860,7 @@
         <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
@@ -2887,24 +2872,24 @@
         <v>136</v>
       </c>
       <c r="I14" t="s">
+        <v>196</v>
+      </c>
+      <c r="J14" t="s">
         <v>197</v>
       </c>
-      <c r="J14" t="s">
-        <v>198</v>
-      </c>
       <c r="K14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L14" t="s">
         <v>140</v>
       </c>
       <c r="M14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B15" t="s">
         <v>132</v>
@@ -2916,7 +2901,7 @@
         <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
@@ -2934,18 +2919,18 @@
         <v>152</v>
       </c>
       <c r="K15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L15" t="s">
         <v>148</v>
       </c>
       <c r="N15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B16" t="s">
         <v>132</v>
@@ -2957,39 +2942,39 @@
         <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
+        <v>220</v>
+      </c>
+      <c r="H16" t="s">
         <v>221</v>
-      </c>
-      <c r="H16" t="s">
-        <v>222</v>
       </c>
       <c r="I16" t="s">
         <v>137</v>
       </c>
       <c r="J16" t="s">
+        <v>222</v>
+      </c>
+      <c r="K16" t="s">
         <v>223</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>224</v>
       </c>
-      <c r="L16" t="s">
+      <c r="M16" t="s">
+        <v>222</v>
+      </c>
+      <c r="N16" t="s">
         <v>225</v>
-      </c>
-      <c r="M16" t="s">
-        <v>223</v>
-      </c>
-      <c r="N16" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B17" t="s">
         <v>132</v>
@@ -3001,7 +2986,7 @@
         <v>34</v>
       </c>
       <c r="E17" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
@@ -3019,7 +3004,7 @@
         <v>146</v>
       </c>
       <c r="K17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L17" t="s">
         <v>148</v>
@@ -3027,7 +3012,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B18" t="s">
         <v>132</v>
@@ -3039,7 +3024,7 @@
         <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
@@ -3057,18 +3042,18 @@
         <v>152</v>
       </c>
       <c r="K18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L18" t="s">
         <v>148</v>
       </c>
       <c r="N18" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>233</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>234</v>
       </c>
       <c r="B19" t="s">
         <v>132</v>
@@ -3080,7 +3065,7 @@
         <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
@@ -3095,33 +3080,30 @@
         <v>137</v>
       </c>
       <c r="J19" t="s">
+        <v>235</v>
+      </c>
+      <c r="K19" t="s">
         <v>236</v>
-      </c>
-      <c r="K19" t="s">
-        <v>237</v>
       </c>
       <c r="L19" t="s">
         <v>164</v>
       </c>
       <c r="M19" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="N19" t="s">
+        <v>237</v>
+      </c>
+      <c r="O19" t="s">
         <v>238</v>
       </c>
-      <c r="O19" t="s">
+      <c r="P19" t="s">
         <v>239</v>
-      </c>
-      <c r="P19" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B20" t="s">
         <v>132</v>
@@ -3133,37 +3115,37 @@
         <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
       </c>
       <c r="G20" t="s">
+        <v>242</v>
+      </c>
+      <c r="H20" t="s">
+        <v>243</v>
+      </c>
+      <c r="I20" t="s">
+        <v>196</v>
+      </c>
+      <c r="J20" t="s">
         <v>244</v>
       </c>
-      <c r="H20" t="s">
+      <c r="K20" t="s">
         <v>245</v>
       </c>
-      <c r="I20" t="s">
-        <v>197</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="L20" t="s">
         <v>246</v>
       </c>
-      <c r="K20" t="s">
+      <c r="M20" t="s">
         <v>247</v>
       </c>
-      <c r="L20" t="s">
+      <c r="N20" t="s">
         <v>248</v>
       </c>
-      <c r="M20" t="s">
+      <c r="O20" t="s">
         <v>249</v>
-      </c>
-      <c r="N20" t="s">
-        <v>250</v>
-      </c>
-      <c r="O20" t="s">
-        <v>251</v>
       </c>
       <c r="P20" t="s">
         <v>185</v>
@@ -3171,7 +3153,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B21" t="s">
         <v>132</v>
@@ -3183,7 +3165,7 @@
         <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
@@ -3201,18 +3183,18 @@
         <v>146</v>
       </c>
       <c r="K21" t="s">
+        <v>252</v>
+      </c>
+      <c r="L21" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q21" t="s">
         <v>254</v>
-      </c>
-      <c r="L21" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B22" t="s">
         <v>132</v>
@@ -3224,7 +3206,7 @@
         <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
@@ -3242,7 +3224,7 @@
         <v>146</v>
       </c>
       <c r="K22" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="L22" t="s">
         <v>148</v>
@@ -3250,7 +3232,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B23" t="s">
         <v>132</v>
@@ -3262,7 +3244,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
@@ -3280,18 +3262,18 @@
         <v>152</v>
       </c>
       <c r="K23" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="L23" t="s">
         <v>148</v>
       </c>
       <c r="N23" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B24" t="s">
         <v>132</v>
@@ -3303,7 +3285,7 @@
         <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F24" t="s">
         <v>13</v>
@@ -3318,33 +3300,30 @@
         <v>137</v>
       </c>
       <c r="J24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="K24" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="L24" t="s">
         <v>164</v>
       </c>
       <c r="M24" t="s">
+        <v>264</v>
+      </c>
+      <c r="N24" t="s">
         <v>266</v>
       </c>
-      <c r="N24" t="s">
+      <c r="O24" t="s">
+        <v>267</v>
+      </c>
+      <c r="P24" t="s">
         <v>268</v>
       </c>
-      <c r="O24" t="s">
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>269</v>
-      </c>
-      <c r="P24" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>272</v>
       </c>
       <c r="B25" t="s">
         <v>132</v>
@@ -3356,7 +3335,7 @@
         <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
@@ -3371,33 +3350,30 @@
         <v>137</v>
       </c>
       <c r="J25" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="K25" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="L25" t="s">
         <v>164</v>
       </c>
       <c r="M25" t="s">
+        <v>271</v>
+      </c>
+      <c r="N25" t="s">
+        <v>273</v>
+      </c>
+      <c r="O25" t="s">
         <v>274</v>
       </c>
-      <c r="N25" t="s">
-        <v>276</v>
-      </c>
-      <c r="O25" t="s">
-        <v>277</v>
-      </c>
       <c r="P25" t="s">
-        <v>278</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B26" t="s">
         <v>132</v>
@@ -3409,7 +3385,7 @@
         <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
@@ -3427,7 +3403,7 @@
         <v>146</v>
       </c>
       <c r="K26" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L26" t="s">
         <v>148</v>
@@ -3435,7 +3411,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B27" t="s">
         <v>132</v>
@@ -3447,7 +3423,7 @@
         <v>34</v>
       </c>
       <c r="E27" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
@@ -3465,18 +3441,18 @@
         <v>152</v>
       </c>
       <c r="K27" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="L27" t="s">
         <v>148</v>
       </c>
       <c r="N27" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B28" t="s">
         <v>132</v>
@@ -3488,7 +3464,7 @@
         <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
@@ -3506,7 +3482,7 @@
         <v>146</v>
       </c>
       <c r="K28" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="L28" t="s">
         <v>148</v>
@@ -3514,7 +3490,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s">
         <v>132</v>
@@ -3526,7 +3502,7 @@
         <v>34</v>
       </c>
       <c r="E29" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
@@ -3544,18 +3520,18 @@
         <v>152</v>
       </c>
       <c r="K29" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="L29" t="s">
         <v>148</v>
       </c>
       <c r="N29" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B30" t="s">
         <v>132</v>
@@ -3567,7 +3543,7 @@
         <v>34</v>
       </c>
       <c r="E30" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
@@ -3585,7 +3561,7 @@
         <v>146</v>
       </c>
       <c r="K30" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="L30" t="s">
         <v>148</v>
@@ -3593,7 +3569,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B31" t="s">
         <v>132</v>
@@ -3605,7 +3581,7 @@
         <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F31" t="s">
         <v>13</v>
@@ -3623,18 +3599,18 @@
         <v>152</v>
       </c>
       <c r="K31" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="L31" t="s">
         <v>148</v>
       </c>
       <c r="N31" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s">
         <v>132</v>
@@ -3646,7 +3622,7 @@
         <v>34</v>
       </c>
       <c r="E32" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
@@ -3664,18 +3640,18 @@
         <v>152</v>
       </c>
       <c r="K32" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="L32" t="s">
         <v>148</v>
       </c>
       <c r="N32" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B33" t="s">
         <v>132</v>
@@ -3687,7 +3663,7 @@
         <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F33" t="s">
         <v>13</v>
@@ -3705,21 +3681,21 @@
         <v>152</v>
       </c>
       <c r="K33" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="L33" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="N33" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="Q33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s">
         <v>132</v>
@@ -3731,7 +3707,7 @@
         <v>34</v>
       </c>
       <c r="E34" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="F34" t="s">
         <v>13</v>
@@ -3740,16 +3716,16 @@
         <v>160</v>
       </c>
       <c r="H34" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="I34" t="s">
         <v>137</v>
       </c>
       <c r="J34" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="K34" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="L34" t="s">
         <v>164</v>
@@ -3760,7 +3736,7 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s">
         <v>132</v>
@@ -3772,7 +3748,7 @@
         <v>34</v>
       </c>
       <c r="E35" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F35" t="s">
         <v>13</v>
@@ -3787,16 +3763,16 @@
         <v>137</v>
       </c>
       <c r="J35" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="K35" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="L35" t="s">
         <v>164</v>
       </c>
       <c r="O35" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="P35" t="s">
         <v>185</v>
@@ -3804,19 +3780,19 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s">
         <v>132</v>
       </c>
       <c r="C36" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D36" t="s">
         <v>34</v>
       </c>
       <c r="E36" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F36" t="s">
         <v>13</v>
@@ -3825,160 +3801,160 @@
         <v>135</v>
       </c>
       <c r="H36" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I36" t="s">
         <v>137</v>
       </c>
       <c r="J36" t="s">
+        <v>315</v>
+      </c>
+      <c r="K36" t="s">
         <v>319</v>
       </c>
-      <c r="K36" t="s">
-        <v>323</v>
-      </c>
       <c r="M36" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="R36" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="S36" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B37" t="s">
         <v>132</v>
       </c>
       <c r="C37" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D37" t="s">
         <v>34</v>
       </c>
       <c r="E37" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="F37" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G37" t="s">
         <v>135</v>
       </c>
       <c r="H37" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="I37" t="s">
         <v>137</v>
       </c>
       <c r="J37" t="s">
+        <v>323</v>
+      </c>
+      <c r="L37" t="s">
         <v>327</v>
       </c>
-      <c r="L37" t="s">
-        <v>331</v>
-      </c>
       <c r="M37" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="R37" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="S37" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B38" t="s">
         <v>132</v>
       </c>
       <c r="C38" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D38" t="s">
         <v>34</v>
       </c>
       <c r="E38" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G38" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="H38" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="I38" t="s">
         <v>137</v>
       </c>
       <c r="J38" t="s">
+        <v>329</v>
+      </c>
+      <c r="K38" t="s">
         <v>333</v>
       </c>
-      <c r="K38" t="s">
-        <v>337</v>
-      </c>
       <c r="L38" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M38" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="R38" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="S38" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B39" t="s">
         <v>132</v>
       </c>
       <c r="C39" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D39" t="s">
         <v>34</v>
       </c>
       <c r="E39" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="F39" t="s">
         <v>13</v>
       </c>
       <c r="G39" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="H39" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="I39" t="s">
         <v>137</v>
       </c>
       <c r="J39" t="s">
+        <v>337</v>
+      </c>
+      <c r="K39" t="s">
+        <v>339</v>
+      </c>
+      <c r="L39" t="s">
+        <v>334</v>
+      </c>
+      <c r="M39" t="s">
+        <v>340</v>
+      </c>
+      <c r="R39" t="s">
         <v>341</v>
       </c>
-      <c r="K39" t="s">
-        <v>343</v>
-      </c>
-      <c r="L39" t="s">
-        <v>338</v>
-      </c>
-      <c r="M39" t="s">
-        <v>344</v>
-      </c>
-      <c r="R39" t="s">
-        <v>345</v>
-      </c>
       <c r="S39" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -4008,46 +3984,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C3" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B4" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C4" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B5" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C5" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>

--- a/ro-crate/ro-crate-metadata.xlsx
+++ b/ro-crate/ro-crate-metadata.xlsx
@@ -575,31 +575,31 @@
     <t>https://raw.githubusercontent.com/Australian-Text-Analytics-Platform/discursis/master/docs/Discursis%20User%20Guide.pdf</t>
   </si>
   <si>
+    <t>Based on Angus, D., Smith, A. E., &amp; Wiles, J. (2012). Human Communication as Coupled Time Series: Quantifying Multi-Participant Recurrence. IEEE Transactions on Audio, Speech, and Language Processing, 20(6), 1795–1807. https://doi.org/10.1109/TASL.2012.2189566</t>
+  </si>
+  <si>
+    <t>arcp://name,DocumentSimilarity</t>
+  </si>
+  <si>
+    <t>Document Similarity</t>
+  </si>
+  <si>
+    <t>["#SonyJufri", "https://orcid.org/0000-0002-1428-2649"]</t>
+  </si>
+  <si>
+    <t>https://github.com/Australian-Text-Analytics-Platform/document-similarity</t>
+  </si>
+  <si>
+    <t>Identifies identical and similar text in a corpus</t>
+  </si>
+  <si>
+    <t>"images/document-similarity.png"</t>
+  </si>
+  <si>
+    <t>https://github.com/Australian-Text-Analytics-Platform/document-similarity/blob/main/documents/docsim-help-pages.pdf</t>
+  </si>
+  <si>
     <t>object Object</t>
-  </si>
-  <si>
-    <t>arcp://name,DocumentSimilarity</t>
-  </si>
-  <si>
-    <t>Document Similarity</t>
-  </si>
-  <si>
-    <t>["#SonyJufri", "https://orcid.org/0000-0002-1428-2649"]</t>
-  </si>
-  <si>
-    <t>https://github.com/Australian-Text-Analytics-Platform/document-similarity</t>
-  </si>
-  <si>
-    <t>Identifies identical and similar text in a corpus</t>
-  </si>
-  <si>
-    <t>"images/document-similarity.png"</t>
-  </si>
-  <si>
-    <t>https://github.com/Australian-Text-Analytics-Platform/document-similarity/blob/main/documents/docsim-help-pages.pdf</t>
-  </si>
-  <si>
-    <t>Jufri, Sony &amp; Sun, Chao (2024). Document Similarity. v1.2. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/document-similarity</t>
   </si>
   <si>
     <t>arcp://name,ELANAnnotationSplitter</t>
@@ -3148,7 +3148,7 @@
         <v>249</v>
       </c>
       <c r="P20" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -3731,7 +3731,7 @@
         <v>164</v>
       </c>
       <c r="P34" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -3775,7 +3775,7 @@
         <v>314</v>
       </c>
       <c r="P35" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">

--- a/ro-crate/ro-crate-metadata.xlsx
+++ b/ro-crate/ro-crate-metadata.xlsx
@@ -575,7 +575,7 @@
     <t>https://raw.githubusercontent.com/Australian-Text-Analytics-Platform/discursis/master/docs/Discursis%20User%20Guide.pdf</t>
   </si>
   <si>
-    <t>Based on Angus, D., Smith, A. E., &amp; Wiles, J. (2012). Human Communication as Coupled Time Series: Quantifying Multi-Participant Recurrence. IEEE Transactions on Audio, Speech, and Language Processing, 20(6), 1795–1807. https://doi.org/10.1109/TASL.2012.2189566</t>
+    <t>Read about Discursis on the LDaCA blog (https://www.ldaca.edu.au/resources/posts/discursis/). Based on Angus, D., Smith, A. E., &amp; Wiles, J. (2012). Human Communication as Coupled Time Series: Quantifying Multi-Participant Recurrence. IEEE Transactions on Audio, Speech, and Language Processing, 20(6), 1795–1807. https://doi.org/10.1109/TASL.2012.2189566</t>
   </si>
   <si>
     <t>arcp://name,DocumentSimilarity</t>

--- a/ro-crate/ro-crate-metadata.xlsx
+++ b/ro-crate/ro-crate-metadata.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="355">
   <si>
     <t>Name</t>
   </si>
@@ -602,6 +602,9 @@
     <t>object Object</t>
   </si>
   <si>
+    <t>Read about the Document Similarity tool on the LDaCA blog (https://www.ldaca.edu.au/resources/posts/similarity-tool/).</t>
+  </si>
+  <si>
     <t>arcp://name,ELANAnnotationSplitter</t>
   </si>
   <si>
@@ -738,6 +741,9 @@
   </si>
   <si>
     <t>Jufri, Sony &amp; Sun, Chao (2022). Keywords Analysis. v1.0. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/keywords-analysis</t>
+  </si>
+  <si>
+    <t>Read about the Keyword Analysis tool on the LDaCA blog (https://www.ldaca.edu.au/resources/posts/keyword-analysis/).</t>
   </si>
   <si>
     <t>arcp://name,Lameta</t>
@@ -828,6 +834,9 @@
     <t>Jufri, Sony &amp; Sun, Chao (2022). Quotation Tool. v1.0. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/quotation-tool</t>
   </si>
   <si>
+    <t>Read about the Quotation tool on the LDaCA blog (https://www.ldaca.edu.au/resources/posts/quotation-tool/).</t>
+  </si>
+  <si>
     <t>arcp://name,SemanticTaggerEnglish</t>
   </si>
   <si>
@@ -847,6 +856,9 @@
   </si>
   <si>
     <t>Jufri, Sony &amp; Sun, Chao (2022). Semantic Tagger. v1.0. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/semantic-tagger</t>
+  </si>
+  <si>
+    <t>Read about the Semantic Tagger on the LDaCA blog (https://www.ldaca.edu.au/resources/posts/semantic-tagger/).</t>
   </si>
   <si>
     <t>arcp://name,SentimentExplorer</t>
@@ -2638,7 +2650,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>186</v>
       </c>
@@ -2687,10 +2699,13 @@
       <c r="P9" t="s">
         <v>193</v>
       </c>
+      <c r="Q9" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B10" t="s">
         <v>132</v>
@@ -2702,7 +2717,7 @@
         <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
@@ -2714,24 +2729,24 @@
         <v>136</v>
       </c>
       <c r="I10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L10" t="s">
         <v>140</v>
       </c>
       <c r="M10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B11" t="s">
         <v>132</v>
@@ -2743,7 +2758,7 @@
         <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
@@ -2755,24 +2770,24 @@
         <v>136</v>
       </c>
       <c r="I11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B12" t="s">
         <v>132</v>
@@ -2784,7 +2799,7 @@
         <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
@@ -2799,10 +2814,10 @@
         <v>151</v>
       </c>
       <c r="J12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L12" t="s">
         <v>140</v>
@@ -2810,7 +2825,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B13" t="s">
         <v>132</v>
@@ -2822,7 +2837,7 @@
         <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
@@ -2837,10 +2852,10 @@
         <v>151</v>
       </c>
       <c r="J13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L13" t="s">
         <v>140</v>
@@ -2848,7 +2863,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B14" t="s">
         <v>132</v>
@@ -2860,7 +2875,7 @@
         <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
@@ -2872,24 +2887,24 @@
         <v>136</v>
       </c>
       <c r="I14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L14" t="s">
         <v>140</v>
       </c>
       <c r="M14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B15" t="s">
         <v>132</v>
@@ -2901,7 +2916,7 @@
         <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
@@ -2919,18 +2934,18 @@
         <v>152</v>
       </c>
       <c r="K15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L15" t="s">
         <v>148</v>
       </c>
       <c r="N15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B16" t="s">
         <v>132</v>
@@ -2942,39 +2957,39 @@
         <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I16" t="s">
         <v>137</v>
       </c>
       <c r="J16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K16" t="s">
+        <v>224</v>
+      </c>
+      <c r="L16" t="s">
+        <v>225</v>
+      </c>
+      <c r="M16" t="s">
         <v>223</v>
       </c>
-      <c r="L16" t="s">
-        <v>224</v>
-      </c>
-      <c r="M16" t="s">
-        <v>222</v>
-      </c>
       <c r="N16" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B17" t="s">
         <v>132</v>
@@ -2986,7 +3001,7 @@
         <v>34</v>
       </c>
       <c r="E17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
@@ -3004,7 +3019,7 @@
         <v>146</v>
       </c>
       <c r="K17" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L17" t="s">
         <v>148</v>
@@ -3012,7 +3027,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B18" t="s">
         <v>132</v>
@@ -3024,7 +3039,7 @@
         <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
@@ -3042,18 +3057,18 @@
         <v>152</v>
       </c>
       <c r="K18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L18" t="s">
         <v>148</v>
       </c>
       <c r="N18" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B19" t="s">
         <v>132</v>
@@ -3065,7 +3080,7 @@
         <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
@@ -3080,30 +3095,33 @@
         <v>137</v>
       </c>
       <c r="J19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K19" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L19" t="s">
         <v>164</v>
       </c>
       <c r="M19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N19" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O19" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P19" t="s">
-        <v>239</v>
+        <v>240</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B20" t="s">
         <v>132</v>
@@ -3115,37 +3133,37 @@
         <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H20" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J20" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K20" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L20" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M20" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N20" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O20" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P20" t="s">
         <v>193</v>
@@ -3153,7 +3171,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B21" t="s">
         <v>132</v>
@@ -3165,7 +3183,7 @@
         <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
@@ -3183,18 +3201,18 @@
         <v>146</v>
       </c>
       <c r="K21" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L21" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q21" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B22" t="s">
         <v>132</v>
@@ -3206,7 +3224,7 @@
         <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
@@ -3224,7 +3242,7 @@
         <v>146</v>
       </c>
       <c r="K22" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L22" t="s">
         <v>148</v>
@@ -3232,7 +3250,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B23" t="s">
         <v>132</v>
@@ -3244,7 +3262,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
@@ -3262,18 +3280,18 @@
         <v>152</v>
       </c>
       <c r="K23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L23" t="s">
         <v>148</v>
       </c>
       <c r="N23" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B24" t="s">
         <v>132</v>
@@ -3285,7 +3303,7 @@
         <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F24" t="s">
         <v>13</v>
@@ -3300,30 +3318,33 @@
         <v>137</v>
       </c>
       <c r="J24" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K24" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L24" t="s">
         <v>164</v>
       </c>
       <c r="M24" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N24" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O24" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P24" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B25" t="s">
         <v>132</v>
@@ -3335,7 +3356,7 @@
         <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
@@ -3350,30 +3371,33 @@
         <v>137</v>
       </c>
       <c r="J25" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K25" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="L25" t="s">
         <v>164</v>
       </c>
       <c r="M25" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="N25" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O25" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="P25" t="s">
-        <v>275</v>
+        <v>278</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B26" t="s">
         <v>132</v>
@@ -3385,7 +3409,7 @@
         <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
@@ -3403,7 +3427,7 @@
         <v>146</v>
       </c>
       <c r="K26" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="L26" t="s">
         <v>148</v>
@@ -3411,7 +3435,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B27" t="s">
         <v>132</v>
@@ -3423,7 +3447,7 @@
         <v>34</v>
       </c>
       <c r="E27" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
@@ -3441,18 +3465,18 @@
         <v>152</v>
       </c>
       <c r="K27" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="L27" t="s">
         <v>148</v>
       </c>
       <c r="N27" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B28" t="s">
         <v>132</v>
@@ -3464,7 +3488,7 @@
         <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
@@ -3482,7 +3506,7 @@
         <v>146</v>
       </c>
       <c r="K28" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="L28" t="s">
         <v>148</v>
@@ -3490,7 +3514,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B29" t="s">
         <v>132</v>
@@ -3502,7 +3526,7 @@
         <v>34</v>
       </c>
       <c r="E29" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
@@ -3520,18 +3544,18 @@
         <v>152</v>
       </c>
       <c r="K29" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="L29" t="s">
         <v>148</v>
       </c>
       <c r="N29" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B30" t="s">
         <v>132</v>
@@ -3543,7 +3567,7 @@
         <v>34</v>
       </c>
       <c r="E30" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
@@ -3561,7 +3585,7 @@
         <v>146</v>
       </c>
       <c r="K30" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="L30" t="s">
         <v>148</v>
@@ -3569,7 +3593,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B31" t="s">
         <v>132</v>
@@ -3581,7 +3605,7 @@
         <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F31" t="s">
         <v>13</v>
@@ -3599,18 +3623,18 @@
         <v>152</v>
       </c>
       <c r="K31" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="L31" t="s">
         <v>148</v>
       </c>
       <c r="N31" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B32" t="s">
         <v>132</v>
@@ -3622,7 +3646,7 @@
         <v>34</v>
       </c>
       <c r="E32" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
@@ -3640,18 +3664,18 @@
         <v>152</v>
       </c>
       <c r="K32" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="L32" t="s">
         <v>148</v>
       </c>
       <c r="N32" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B33" t="s">
         <v>132</v>
@@ -3663,7 +3687,7 @@
         <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="F33" t="s">
         <v>13</v>
@@ -3681,21 +3705,21 @@
         <v>152</v>
       </c>
       <c r="K33" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="L33" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N33" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q33" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B34" t="s">
         <v>132</v>
@@ -3707,7 +3731,7 @@
         <v>34</v>
       </c>
       <c r="E34" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F34" t="s">
         <v>13</v>
@@ -3716,16 +3740,16 @@
         <v>160</v>
       </c>
       <c r="H34" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I34" t="s">
         <v>137</v>
       </c>
       <c r="J34" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="K34" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="L34" t="s">
         <v>164</v>
@@ -3736,7 +3760,7 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B35" t="s">
         <v>132</v>
@@ -3748,7 +3772,7 @@
         <v>34</v>
       </c>
       <c r="E35" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F35" t="s">
         <v>13</v>
@@ -3763,16 +3787,16 @@
         <v>137</v>
       </c>
       <c r="J35" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="K35" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="L35" t="s">
         <v>164</v>
       </c>
       <c r="O35" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="P35" t="s">
         <v>193</v>
@@ -3780,19 +3804,19 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B36" t="s">
         <v>132</v>
       </c>
       <c r="C36" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D36" t="s">
         <v>34</v>
       </c>
       <c r="E36" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="F36" t="s">
         <v>13</v>
@@ -3801,160 +3825,160 @@
         <v>135</v>
       </c>
       <c r="H36" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="I36" t="s">
         <v>137</v>
       </c>
       <c r="J36" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="K36" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="M36" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="R36" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="S36" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s">
         <v>132</v>
       </c>
       <c r="C37" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D37" t="s">
         <v>34</v>
       </c>
       <c r="E37" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F37" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G37" t="s">
         <v>135</v>
       </c>
       <c r="H37" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="I37" t="s">
         <v>137</v>
       </c>
       <c r="J37" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L37" t="s">
+        <v>331</v>
+      </c>
+      <c r="M37" t="s">
         <v>327</v>
       </c>
-      <c r="M37" t="s">
-        <v>323</v>
-      </c>
       <c r="R37" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="S37" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B38" t="s">
         <v>132</v>
       </c>
       <c r="C38" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D38" t="s">
         <v>34</v>
       </c>
       <c r="E38" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="G38" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="H38" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I38" t="s">
         <v>137</v>
       </c>
       <c r="J38" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K38" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="L38" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="M38" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="R38" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="S38" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B39" t="s">
         <v>132</v>
       </c>
       <c r="C39" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D39" t="s">
         <v>34</v>
       </c>
       <c r="E39" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F39" t="s">
         <v>13</v>
       </c>
       <c r="G39" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="H39" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I39" t="s">
         <v>137</v>
       </c>
       <c r="J39" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="K39" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="L39" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="M39" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="R39" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="S39" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -3984,46 +4008,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C4" t="s">
         <v>348</v>
-      </c>
-      <c r="C4" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C5" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>

--- a/ro-crate/ro-crate-metadata.xlsx
+++ b/ro-crate/ro-crate-metadata.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="358">
   <si>
     <t>Name</t>
   </si>
@@ -599,7 +599,7 @@
     <t>https://github.com/Australian-Text-Analytics-Platform/document-similarity/blob/main/documents/docsim-help-pages.pdf</t>
   </si>
   <si>
-    <t>object Object</t>
+    <t>Jufri, Sony &amp; Sun, Chao (2024). Document Similarity. v1.2. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/document-similarity</t>
   </si>
   <si>
     <t>Read about the Document Similarity tool on the LDaCA blog (https://www.ldaca.edu.au/resources/posts/similarity-tool/).</t>
@@ -777,6 +777,9 @@
     <t>https://www.elararchive.org/uncategorized/SO_7557c4dd-1c83-485c-b95c-c0a292cfc42c/</t>
   </si>
   <si>
+    <t>Hatton, John, Gary Holton, Mandana Seyfeddinipur, Nick Thieberger. 2021. Lameta [software] https://github.com/onset/laMETA/releases</t>
+  </si>
+  <si>
     <t>arcp://name,NetworkVisualiser</t>
   </si>
   <si>
@@ -963,6 +966,9 @@
     <t>Topic modelling approach that infers a hierarchy of topic clusters and word clusters in your Corpus in a non-parametric manner by leveraging stochastic block models.</t>
   </si>
   <si>
+    <t>Chan, Huen Hei &amp; Altmann, Eduardo G. (2024) TopSBM. v1.0. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/topsbm</t>
+  </si>
+  <si>
     <t>arcp://name,SemanticTaggermultilingual</t>
   </si>
   <si>
@@ -976,6 +982,9 @@
   </si>
   <si>
     <t>https://github.com/Australian-Text-Analytics-Platform/semantic-tagger/blob/multi-lingual/documents/semtag_help_pages.pdf</t>
+  </si>
+  <si>
+    <t>Jufri, Sony &amp; Sun, Chao (2022). Semantic Tagger (Multi-Lingual). v1.0. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/semantic-tagger/tree/multi-lingual</t>
   </si>
   <si>
     <t>https://data.ldaca.edu.au/object?_id=https://github.com/Australian-Text-Analytics-Platform/cooee/blob/main/cooee.ipynb</t>
@@ -3166,12 +3175,12 @@
         <v>251</v>
       </c>
       <c r="P20" t="s">
-        <v>193</v>
+        <v>252</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B21" t="s">
         <v>132</v>
@@ -3183,7 +3192,7 @@
         <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
@@ -3201,18 +3210,18 @@
         <v>146</v>
       </c>
       <c r="K21" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L21" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q21" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B22" t="s">
         <v>132</v>
@@ -3224,7 +3233,7 @@
         <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
@@ -3242,7 +3251,7 @@
         <v>146</v>
       </c>
       <c r="K22" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L22" t="s">
         <v>148</v>
@@ -3250,7 +3259,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B23" t="s">
         <v>132</v>
@@ -3262,7 +3271,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
@@ -3280,18 +3289,18 @@
         <v>152</v>
       </c>
       <c r="K23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L23" t="s">
         <v>148</v>
       </c>
       <c r="N23" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B24" t="s">
         <v>132</v>
@@ -3303,7 +3312,7 @@
         <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F24" t="s">
         <v>13</v>
@@ -3318,33 +3327,33 @@
         <v>137</v>
       </c>
       <c r="J24" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K24" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L24" t="s">
         <v>164</v>
       </c>
       <c r="M24" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N24" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O24" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P24" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q24" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B25" t="s">
         <v>132</v>
@@ -3356,7 +3365,7 @@
         <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
@@ -3371,33 +3380,33 @@
         <v>137</v>
       </c>
       <c r="J25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K25" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L25" t="s">
         <v>164</v>
       </c>
       <c r="M25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N25" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O25" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P25" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q25" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B26" t="s">
         <v>132</v>
@@ -3409,7 +3418,7 @@
         <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
@@ -3427,7 +3436,7 @@
         <v>146</v>
       </c>
       <c r="K26" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L26" t="s">
         <v>148</v>
@@ -3435,7 +3444,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B27" t="s">
         <v>132</v>
@@ -3447,7 +3456,7 @@
         <v>34</v>
       </c>
       <c r="E27" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
@@ -3465,18 +3474,18 @@
         <v>152</v>
       </c>
       <c r="K27" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L27" t="s">
         <v>148</v>
       </c>
       <c r="N27" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B28" t="s">
         <v>132</v>
@@ -3488,7 +3497,7 @@
         <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
@@ -3506,7 +3515,7 @@
         <v>146</v>
       </c>
       <c r="K28" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L28" t="s">
         <v>148</v>
@@ -3514,7 +3523,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B29" t="s">
         <v>132</v>
@@ -3526,7 +3535,7 @@
         <v>34</v>
       </c>
       <c r="E29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
@@ -3544,18 +3553,18 @@
         <v>152</v>
       </c>
       <c r="K29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L29" t="s">
         <v>148</v>
       </c>
       <c r="N29" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B30" t="s">
         <v>132</v>
@@ -3567,7 +3576,7 @@
         <v>34</v>
       </c>
       <c r="E30" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
@@ -3585,7 +3594,7 @@
         <v>146</v>
       </c>
       <c r="K30" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L30" t="s">
         <v>148</v>
@@ -3593,7 +3602,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s">
         <v>132</v>
@@ -3605,7 +3614,7 @@
         <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F31" t="s">
         <v>13</v>
@@ -3623,18 +3632,18 @@
         <v>152</v>
       </c>
       <c r="K31" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L31" t="s">
         <v>148</v>
       </c>
       <c r="N31" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B32" t="s">
         <v>132</v>
@@ -3646,7 +3655,7 @@
         <v>34</v>
       </c>
       <c r="E32" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
@@ -3664,18 +3673,18 @@
         <v>152</v>
       </c>
       <c r="K32" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L32" t="s">
         <v>148</v>
       </c>
       <c r="N32" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s">
         <v>132</v>
@@ -3687,7 +3696,7 @@
         <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F33" t="s">
         <v>13</v>
@@ -3705,21 +3714,21 @@
         <v>152</v>
       </c>
       <c r="K33" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L33" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N33" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q33" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B34" t="s">
         <v>132</v>
@@ -3731,7 +3740,7 @@
         <v>34</v>
       </c>
       <c r="E34" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F34" t="s">
         <v>13</v>
@@ -3740,27 +3749,27 @@
         <v>160</v>
       </c>
       <c r="H34" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I34" t="s">
         <v>137</v>
       </c>
       <c r="J34" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K34" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L34" t="s">
         <v>164</v>
       </c>
       <c r="P34" t="s">
-        <v>193</v>
+        <v>315</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B35" t="s">
         <v>132</v>
@@ -3772,7 +3781,7 @@
         <v>34</v>
       </c>
       <c r="E35" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F35" t="s">
         <v>13</v>
@@ -3787,36 +3796,36 @@
         <v>137</v>
       </c>
       <c r="J35" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K35" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L35" t="s">
         <v>164</v>
       </c>
       <c r="O35" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P35" t="s">
-        <v>193</v>
+        <v>321</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B36" t="s">
         <v>132</v>
       </c>
       <c r="C36" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D36" t="s">
         <v>34</v>
       </c>
       <c r="E36" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F36" t="s">
         <v>13</v>
@@ -3825,160 +3834,160 @@
         <v>135</v>
       </c>
       <c r="H36" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="I36" t="s">
         <v>137</v>
       </c>
       <c r="J36" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="K36" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="M36" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="R36" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="S36" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B37" t="s">
         <v>132</v>
       </c>
       <c r="C37" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D37" t="s">
         <v>34</v>
       </c>
       <c r="E37" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F37" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G37" t="s">
         <v>135</v>
       </c>
       <c r="H37" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="I37" t="s">
         <v>137</v>
       </c>
       <c r="J37" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="L37" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="M37" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="R37" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="S37" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s">
         <v>132</v>
       </c>
       <c r="C38" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D38" t="s">
         <v>34</v>
       </c>
       <c r="E38" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G38" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H38" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I38" t="s">
         <v>137</v>
       </c>
       <c r="J38" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K38" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="L38" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="M38" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="R38" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="S38" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B39" t="s">
         <v>132</v>
       </c>
       <c r="C39" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D39" t="s">
         <v>34</v>
       </c>
       <c r="E39" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F39" t="s">
         <v>13</v>
       </c>
       <c r="G39" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H39" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I39" t="s">
         <v>137</v>
       </c>
       <c r="J39" t="s">
+        <v>344</v>
+      </c>
+      <c r="K39" t="s">
+        <v>346</v>
+      </c>
+      <c r="L39" t="s">
         <v>341</v>
       </c>
-      <c r="K39" t="s">
-        <v>343</v>
-      </c>
-      <c r="L39" t="s">
-        <v>338</v>
-      </c>
       <c r="M39" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="R39" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="S39" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -4008,46 +4017,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B3" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C3" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>354</v>
+      </c>
+      <c r="B4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C4" t="s">
         <v>351</v>
-      </c>
-      <c r="B4" t="s">
-        <v>352</v>
-      </c>
-      <c r="C4" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B5" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C5" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>

--- a/ro-crate/ro-crate-metadata.xlsx
+++ b/ro-crate/ro-crate-metadata.xlsx
@@ -575,7 +575,7 @@
     <t>https://raw.githubusercontent.com/Australian-Text-Analytics-Platform/discursis/master/docs/Discursis%20User%20Guide.pdf</t>
   </si>
   <si>
-    <t>Read about Discursis on the LDaCA blog (https://www.ldaca.edu.au/resources/posts/discursis/). Based on Angus, D., Smith, A. E., &amp; Wiles, J. (2012). Human Communication as Coupled Time Series: Quantifying Multi-Participant Recurrence. IEEE Transactions on Audio, Speech, and Language Processing, 20(6), 1795–1807. https://doi.org/10.1109/TASL.2012.2189566</t>
+    <t>Read about Discursis on the LDaCA blog (https://www.ldaca.edu.au/news/posts/discursis/). Based on Angus, D., Smith, A. E., &amp; Wiles, J. (2012). Human Communication as Coupled Time Series: Quantifying Multi-Participant Recurrence. IEEE Transactions on Audio, Speech, and Language Processing, 20(6), 1795–1807. https://doi.org/10.1109/TASL.2012.2189566</t>
   </si>
   <si>
     <t>arcp://name,DocumentSimilarity</t>
@@ -602,7 +602,7 @@
     <t>Jufri, Sony &amp; Sun, Chao (2024). Document Similarity. v1.2. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/document-similarity</t>
   </si>
   <si>
-    <t>Read about the Document Similarity tool on the LDaCA blog (https://www.ldaca.edu.au/resources/posts/similarity-tool/).</t>
+    <t>Read about the Document Similarity tool on the LDaCA blog (https://www.ldaca.edu.au/news/posts/similarity-tool/).</t>
   </si>
   <si>
     <t>arcp://name,ELANAnnotationSplitter</t>
@@ -743,7 +743,7 @@
     <t>Jufri, Sony &amp; Sun, Chao (2022). Keywords Analysis. v1.0. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/keywords-analysis</t>
   </si>
   <si>
-    <t>Read about the Keyword Analysis tool on the LDaCA blog (https://www.ldaca.edu.au/resources/posts/keyword-analysis/).</t>
+    <t>Read about the Keyword Analysis tool on the LDaCA blog (https://www.ldaca.edu.au/news/posts/keyword-analysis/).</t>
   </si>
   <si>
     <t>arcp://name,Lameta</t>
@@ -837,7 +837,7 @@
     <t>Jufri, Sony &amp; Sun, Chao (2022). Quotation Tool. v1.0. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/quotation-tool</t>
   </si>
   <si>
-    <t>Read about the Quotation tool on the LDaCA blog (https://www.ldaca.edu.au/resources/posts/quotation-tool/).</t>
+    <t>Read about the Quotation tool on the LDaCA blog (https://www.ldaca.edu.au/news/posts/quotation-tool/).</t>
   </si>
   <si>
     <t>arcp://name,SemanticTaggerEnglish</t>
@@ -861,7 +861,7 @@
     <t>Jufri, Sony &amp; Sun, Chao (2022). Semantic Tagger. v1.0. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/semantic-tagger</t>
   </si>
   <si>
-    <t>Read about the Semantic Tagger on the LDaCA blog (https://www.ldaca.edu.au/resources/posts/semantic-tagger/).</t>
+    <t>Read about the Semantic Tagger on the LDaCA blog (https://www.ldaca.edu.au/news/posts/semantic-tagger/).</t>
   </si>
   <si>
     <t>arcp://name,SentimentExplorer</t>
